--- a/reference/thong_ke_dau/test_2_19Aug26.xlsx
+++ b/reference/thong_ke_dau/test_2_19Aug26.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hungnguyen09/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hungnguyen09/Side_Project/PhuPhatCorp/web_v2/reference/thong_ke_dau/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0688E5A-784C-E248-A07B-A0847E656944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4742235E-A143-2B4A-A1A7-BCFD72A6C9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -240,7 +240,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -272,7 +272,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,366 +492,401 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448D2D2D-B13D-024E-8A34-CC190BBE5584}">
-  <dimension ref="A2:R360"/>
+  <dimension ref="A1:R359"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
+      <c r="A2" s="1">
+        <v>46235</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>211087</v>
+      </c>
+      <c r="D2">
+        <v>211335</v>
+      </c>
+      <c r="E2">
+        <v>248</v>
+      </c>
+      <c r="F2">
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>16.129032258064516</v>
+      </c>
+      <c r="H2">
+        <v>41545</v>
+      </c>
+      <c r="I2">
+        <v>41811</v>
+      </c>
+      <c r="J2">
+        <v>266</v>
+      </c>
+      <c r="K2">
+        <v>40</v>
+      </c>
+      <c r="L2">
+        <v>15.037593984962406</v>
+      </c>
+      <c r="M2">
+        <v>27620</v>
+      </c>
+      <c r="N2">
+        <v>1104800</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>211087</v>
+        <v>211335</v>
       </c>
       <c r="D3">
-        <v>211335</v>
+        <v>211631</v>
       </c>
       <c r="E3">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>16.129032258064516</v>
+        <v>10.135135135135135</v>
       </c>
       <c r="H3">
-        <v>41545</v>
+        <v>41811</v>
       </c>
       <c r="I3">
-        <v>41811</v>
+        <v>42119</v>
       </c>
       <c r="J3">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L3">
-        <v>15.037593984962406</v>
+        <v>9.7402597402597415</v>
       </c>
       <c r="M3">
         <v>27620</v>
       </c>
       <c r="N3">
-        <v>1104800</v>
+        <v>828600</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3">
+        <v>2730140</v>
+      </c>
+      <c r="R3">
+        <v>2730140</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>211335</v>
+        <v>211631</v>
       </c>
       <c r="D4">
-        <v>211631</v>
+        <v>211794</v>
       </c>
       <c r="E4">
-        <v>296</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
       <c r="G4">
-        <v>10.135135135135135</v>
+        <v>18.404907975460123</v>
       </c>
       <c r="H4">
-        <v>41811</v>
+        <v>42119</v>
       </c>
       <c r="I4">
-        <v>42119</v>
+        <v>42298</v>
       </c>
       <c r="J4">
-        <v>308</v>
+        <v>179</v>
       </c>
       <c r="K4">
         <v>30</v>
       </c>
       <c r="L4">
-        <v>9.7402597402597415</v>
+        <v>16.759776536312849</v>
       </c>
       <c r="M4">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N4">
-        <v>828600</v>
+        <v>826200</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>2730140</v>
+        <v>5192920</v>
       </c>
       <c r="R4">
-        <v>2730140</v>
+        <v>5192920</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>211631</v>
+        <v>211794</v>
       </c>
       <c r="D5">
-        <v>211794</v>
+        <v>212111</v>
       </c>
       <c r="E5">
-        <v>163</v>
+        <v>317</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G5">
-        <v>18.404907975460123</v>
+        <v>14.195583596214512</v>
       </c>
       <c r="H5">
-        <v>42119</v>
+        <v>42298</v>
       </c>
       <c r="I5">
-        <v>42298</v>
+        <v>42578</v>
       </c>
       <c r="J5">
-        <v>179</v>
+        <v>280</v>
       </c>
       <c r="K5">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="L5">
-        <v>16.759776536312849</v>
+        <v>16.071428571428573</v>
       </c>
       <c r="M5">
         <v>27540</v>
       </c>
       <c r="N5">
-        <v>826200</v>
+        <v>1239300</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q5">
-        <v>5192920</v>
+        <v>4672600</v>
       </c>
       <c r="R5">
-        <v>5192920</v>
+        <v>4672600</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6">
-        <v>211794</v>
+        <v>212111</v>
       </c>
       <c r="D6">
-        <v>212111</v>
+        <v>212436</v>
       </c>
       <c r="E6">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F6">
         <v>45</v>
       </c>
       <c r="G6">
-        <v>14.195583596214512</v>
+        <v>13.846153846153847</v>
       </c>
       <c r="H6">
-        <v>42298</v>
+        <v>42578</v>
       </c>
       <c r="I6">
-        <v>42578</v>
+        <v>42891</v>
       </c>
       <c r="J6">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="K6">
         <v>45</v>
       </c>
       <c r="L6">
-        <v>16.071428571428573</v>
+        <v>14.376996805111823</v>
       </c>
       <c r="M6">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N6">
-        <v>1239300</v>
+        <v>1225350</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q6">
-        <v>4672600</v>
+        <v>3542620</v>
       </c>
       <c r="R6">
-        <v>4672600</v>
+        <v>3542620</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7">
-        <v>212111</v>
+        <v>212436</v>
       </c>
       <c r="D7">
-        <v>212436</v>
+        <v>212707</v>
       </c>
       <c r="E7">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>13.846153846153847</v>
+        <v>14.760147601476014</v>
       </c>
       <c r="H7">
-        <v>42578</v>
+        <v>42891</v>
       </c>
       <c r="I7">
-        <v>42891</v>
+        <v>43184</v>
       </c>
       <c r="J7">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L7">
-        <v>14.376996805111823</v>
+        <v>13.651877133105803</v>
       </c>
       <c r="M7">
         <v>27230</v>
       </c>
       <c r="N7">
-        <v>1225350</v>
+        <v>1089200</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q7">
-        <v>3542620</v>
+        <v>1143660</v>
       </c>
       <c r="R7">
-        <v>3542620</v>
+        <v>1143660</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
-        <v>46252</v>
-      </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>212436</v>
-      </c>
-      <c r="D8">
-        <v>212707</v>
-      </c>
       <c r="E8">
-        <v>271</v>
-      </c>
-      <c r="F8">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>14.760147601476014</v>
-      </c>
-      <c r="H8">
-        <v>42891</v>
-      </c>
-      <c r="I8">
-        <v>43184</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J8">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>40</v>
-      </c>
-      <c r="L8">
-        <v>13.651877133105803</v>
-      </c>
-      <c r="M8">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L8" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N8">
-        <v>1089200</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q8">
-        <v>1143660</v>
+        <v>6313450</v>
       </c>
       <c r="R8">
-        <v>1143660</v>
+        <v>6313450</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -877,198 +912,198 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q9">
+        <v>5303560</v>
+      </c>
+      <c r="R9">
+        <v>5303560</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>1620</v>
+      </c>
+      <c r="G10" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10">
+        <v>1639</v>
+      </c>
+      <c r="K10">
+        <v>230</v>
+      </c>
+      <c r="L10" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10">
         <v>6313450</v>
       </c>
-      <c r="R9">
-        <v>6313450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>7</v>
-      </c>
       <c r="P10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q10">
-        <v>5303560</v>
+        <v>4970480</v>
       </c>
       <c r="R10">
-        <v>5303560</v>
+        <v>4970480</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D11" t="s">
-        <v>16</v>
+      <c r="A11" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>174900</v>
+      </c>
+      <c r="D11">
+        <v>175256</v>
       </c>
       <c r="E11">
-        <v>1620</v>
-      </c>
-      <c r="G11" t="e">
-        <v>#VALUE!</v>
+        <v>356</v>
+      </c>
+      <c r="F11">
+        <v>46</v>
+      </c>
+      <c r="G11">
+        <v>12.921348314606742</v>
+      </c>
+      <c r="H11">
+        <v>43081</v>
+      </c>
+      <c r="I11">
+        <v>43431</v>
       </c>
       <c r="J11">
-        <v>1639</v>
+        <v>350</v>
       </c>
       <c r="K11">
-        <v>230</v>
-      </c>
-      <c r="L11" t="e">
-        <v>#DIV/0!</v>
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>13.142857142857142</v>
+      </c>
+      <c r="M11">
+        <v>27620</v>
       </c>
       <c r="N11">
-        <v>6313450</v>
+        <v>1270520</v>
       </c>
       <c r="O11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q11">
-        <v>4970480</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4970480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>174900</v>
+        <v>175256</v>
       </c>
       <c r="D12">
-        <v>175256</v>
+        <v>175655</v>
       </c>
       <c r="E12">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="F12">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G12">
-        <v>12.921348314606742</v>
+        <v>13.283208020050125</v>
       </c>
       <c r="H12">
-        <v>43081</v>
+        <v>43431</v>
       </c>
       <c r="I12">
-        <v>43431</v>
+        <v>43821</v>
       </c>
       <c r="J12">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="K12">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L12">
-        <v>13.142857142857142</v>
+        <v>13.589743589743589</v>
       </c>
       <c r="M12">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N12">
-        <v>1270520</v>
+        <v>1459620</v>
       </c>
       <c r="O12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4973420</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4973420</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>46246</v>
-      </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13">
-        <v>175256</v>
-      </c>
-      <c r="D13">
-        <v>175655</v>
-      </c>
       <c r="E13">
-        <v>399</v>
-      </c>
-      <c r="F13">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>13.283208020050125</v>
-      </c>
-      <c r="H13">
-        <v>43431</v>
-      </c>
-      <c r="I13">
-        <v>43821</v>
+        <v>0</v>
+      </c>
+      <c r="G13" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J13">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>53</v>
-      </c>
-      <c r="L13">
-        <v>13.589743589743589</v>
-      </c>
-      <c r="M13">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L13" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N13">
-        <v>1459620</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q13">
-        <v>4973420</v>
+        <v>3530320</v>
       </c>
       <c r="R13">
-        <v>4973420</v>
+        <v>3530320</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.15">
@@ -1094,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q14">
-        <v>3530320</v>
+        <v>3805080</v>
       </c>
       <c r="R14">
-        <v>3530320</v>
+        <v>3805080</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.15">
@@ -1129,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15">
-        <v>3805080</v>
+        <v>5766380</v>
       </c>
       <c r="R15">
-        <v>3805080</v>
+        <v>5766380</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
@@ -1164,16 +1199,16 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q16">
-        <v>5766380</v>
+        <v>4922790</v>
       </c>
       <c r="R16">
-        <v>5766380</v>
+        <v>4922790</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
@@ -1199,45 +1234,45 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P17" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="Q17">
-        <v>4922790</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>4922790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B18" t="s">
-        <v>9</v>
+      <c r="D18" t="s">
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="G18" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L18" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2730140</v>
       </c>
       <c r="O18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P18" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -1247,32 +1282,53 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D19" t="s">
-        <v>16</v>
+      <c r="A19" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>190104</v>
+      </c>
+      <c r="D19">
+        <v>190390</v>
       </c>
       <c r="E19">
-        <v>755</v>
-      </c>
-      <c r="G19" t="e">
-        <v>#DIV/0!</v>
+        <v>286</v>
+      </c>
+      <c r="F19">
+        <v>42</v>
+      </c>
+      <c r="G19">
+        <v>14.685314685314685</v>
+      </c>
+      <c r="H19">
+        <v>42572</v>
+      </c>
+      <c r="I19">
+        <v>42897</v>
       </c>
       <c r="J19">
-        <v>740</v>
+        <v>325</v>
       </c>
       <c r="K19">
-        <v>99</v>
-      </c>
-      <c r="L19" t="e">
-        <v>#DIV/0!</v>
+        <v>42</v>
+      </c>
+      <c r="L19">
+        <v>12.923076923076923</v>
+      </c>
+      <c r="M19">
+        <v>27620</v>
       </c>
       <c r="N19">
-        <v>2730140</v>
+        <v>1160040</v>
       </c>
       <c r="O19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -1283,52 +1339,52 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20">
-        <v>190104</v>
+        <v>190390</v>
       </c>
       <c r="D20">
-        <v>190390</v>
+        <v>190716</v>
       </c>
       <c r="E20">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G20">
-        <v>14.685314685314685</v>
+        <v>14.417177914110429</v>
       </c>
       <c r="H20">
-        <v>42572</v>
+        <v>42897</v>
       </c>
       <c r="I20">
-        <v>42897</v>
+        <v>43247</v>
       </c>
       <c r="J20">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="K20">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L20">
-        <v>12.923076923076923</v>
+        <v>13.428571428571429</v>
       </c>
       <c r="M20">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N20">
-        <v>1160040</v>
+        <v>1294380</v>
       </c>
       <c r="O20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P20" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -1339,52 +1395,52 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>190390</v>
+        <v>190716</v>
       </c>
       <c r="D21">
-        <v>190716</v>
+        <v>191063</v>
       </c>
       <c r="E21">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="F21">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G21">
-        <v>14.417177914110429</v>
+        <v>14.409221902017292</v>
       </c>
       <c r="H21">
-        <v>42897</v>
+        <v>43247</v>
       </c>
       <c r="I21">
-        <v>43247</v>
+        <v>43587</v>
       </c>
       <c r="J21">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="K21">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L21">
-        <v>13.428571428571429</v>
+        <v>14.705882352941178</v>
       </c>
       <c r="M21">
         <v>27540</v>
       </c>
       <c r="N21">
-        <v>1294380</v>
+        <v>1377000</v>
       </c>
       <c r="O21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -1395,52 +1451,52 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>190716</v>
+        <v>191063</v>
       </c>
       <c r="D22">
-        <v>191063</v>
+        <v>191402</v>
       </c>
       <c r="E22">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F22">
         <v>50</v>
       </c>
       <c r="G22">
-        <v>14.409221902017292</v>
+        <v>14.749262536873156</v>
       </c>
       <c r="H22">
-        <v>43247</v>
+        <v>43587</v>
       </c>
       <c r="I22">
-        <v>43587</v>
+        <v>43899</v>
       </c>
       <c r="J22">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="K22">
         <v>50</v>
       </c>
       <c r="L22">
-        <v>14.705882352941178</v>
+        <v>16.025641025641026</v>
       </c>
       <c r="M22">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N22">
-        <v>1377000</v>
+        <v>1361500</v>
       </c>
       <c r="O22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -1450,53 +1506,32 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>46252</v>
-      </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="C23">
-        <v>191063</v>
-      </c>
-      <c r="D23">
-        <v>191402</v>
-      </c>
       <c r="E23">
-        <v>339</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>14.749262536873156</v>
-      </c>
-      <c r="H23">
-        <v>43587</v>
-      </c>
-      <c r="I23">
-        <v>43899</v>
+        <v>0</v>
+      </c>
+      <c r="G23" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J23">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>50</v>
-      </c>
-      <c r="L23">
-        <v>16.025641025641026</v>
-      </c>
-      <c r="M23">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L23" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N23">
-        <v>1361500</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -1528,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -1563,16 +1598,16 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3971760</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>3971760</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.15">
@@ -1598,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q26">
-        <v>3971760</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>3971760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.15">
@@ -1633,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -1646,32 +1681,32 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B28" t="s">
-        <v>10</v>
+      <c r="D28" t="s">
+        <v>16</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="G28" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1327</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="L28" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>5192920</v>
       </c>
       <c r="O28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -1681,132 +1716,144 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D29" t="s">
-        <v>16</v>
+      <c r="A29" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29">
+        <v>195947</v>
+      </c>
+      <c r="D29">
+        <v>196260</v>
       </c>
       <c r="E29">
-        <v>1298</v>
-      </c>
-      <c r="G29" t="e">
-        <v>#DIV/0!</v>
+        <v>313</v>
+      </c>
+      <c r="F29">
+        <v>40</v>
+      </c>
+      <c r="G29">
+        <v>12.779552715654951</v>
+      </c>
+      <c r="H29">
+        <v>37593</v>
+      </c>
+      <c r="I29">
+        <v>37913</v>
       </c>
       <c r="J29">
-        <v>1327</v>
+        <v>320</v>
       </c>
       <c r="K29">
-        <v>189</v>
-      </c>
-      <c r="L29" t="e">
-        <v>#DIV/0!</v>
+        <v>40</v>
+      </c>
+      <c r="L29">
+        <v>12.5</v>
+      </c>
+      <c r="M29">
+        <v>27620</v>
       </c>
       <c r="N29">
-        <v>5192920</v>
-      </c>
-      <c r="O29">
-        <v>26</v>
-      </c>
-      <c r="P29" t="s">
-        <v>34</v>
+        <v>1104800</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>60839180</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>60839180</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>195947</v>
+        <v>196260</v>
       </c>
       <c r="D30">
-        <v>196260</v>
+        <v>196636</v>
       </c>
       <c r="E30">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>12.779552715654951</v>
+        <v>13.297872340425531</v>
       </c>
       <c r="H30">
-        <v>37593</v>
+        <v>37913</v>
       </c>
       <c r="I30">
-        <v>37913</v>
+        <v>38213</v>
       </c>
       <c r="J30">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="K30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L30">
-        <v>12.5</v>
+        <v>16.666666666666664</v>
       </c>
       <c r="M30">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N30">
-        <v>1104800</v>
-      </c>
-      <c r="Q30">
-        <v>60839180</v>
+        <v>1377000</v>
       </c>
       <c r="R30">
-        <v>60839180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>196260</v>
+        <v>196636</v>
       </c>
       <c r="D31">
-        <v>196636</v>
+        <v>196991</v>
       </c>
       <c r="E31">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="F31">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G31">
-        <v>13.297872340425531</v>
+        <v>11.267605633802818</v>
       </c>
       <c r="H31">
-        <v>37913</v>
+        <v>38213</v>
       </c>
       <c r="I31">
-        <v>38213</v>
+        <v>38516</v>
       </c>
       <c r="J31">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K31">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L31">
-        <v>16.666666666666664</v>
+        <v>13.201320132013199</v>
       </c>
       <c r="M31">
         <v>27540</v>
       </c>
       <c r="N31">
-        <v>1377000</v>
+        <v>1101600</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -1814,93 +1861,72 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>196636</v>
+        <v>196991</v>
       </c>
       <c r="D32">
-        <v>196991</v>
+        <v>197277</v>
       </c>
       <c r="E32">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="F32">
         <v>40</v>
       </c>
       <c r="G32">
-        <v>11.267605633802818</v>
+        <v>13.986013986013987</v>
       </c>
       <c r="H32">
-        <v>38213</v>
+        <v>38516</v>
       </c>
       <c r="I32">
-        <v>38516</v>
+        <v>38786</v>
       </c>
       <c r="J32">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="L32">
-        <v>13.201320132013199</v>
+        <v>14.814814814814813</v>
       </c>
       <c r="M32">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N32">
-        <v>1101600</v>
+        <v>1089200</v>
       </c>
       <c r="R32">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A33" s="1">
-        <v>46251</v>
-      </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
-      <c r="C33">
-        <v>196991</v>
-      </c>
-      <c r="D33">
-        <v>197277</v>
-      </c>
       <c r="E33">
-        <v>286</v>
-      </c>
-      <c r="F33">
-        <v>40</v>
-      </c>
-      <c r="G33">
-        <v>13.986013986013987</v>
-      </c>
-      <c r="H33">
-        <v>38516</v>
-      </c>
-      <c r="I33">
-        <v>38786</v>
+        <v>0</v>
+      </c>
+      <c r="G33" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J33">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>40</v>
-      </c>
-      <c r="L33">
-        <v>14.814814814814813</v>
-      </c>
-      <c r="M33">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L33" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N33">
-        <v>1089200</v>
+        <v>0</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -1985,52 +2011,73 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B37" t="s">
-        <v>11</v>
+      <c r="D37" t="s">
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1330</v>
       </c>
       <c r="G37" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1193</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L37" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4672600</v>
       </c>
       <c r="R37">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D38" t="s">
-        <v>16</v>
+      <c r="A38" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>185405</v>
+      </c>
+      <c r="D38">
+        <v>185835</v>
       </c>
       <c r="E38">
-        <v>1330</v>
-      </c>
-      <c r="G38" t="e">
-        <v>#DIV/0!</v>
+        <v>430</v>
+      </c>
+      <c r="F38">
+        <v>45</v>
+      </c>
+      <c r="G38">
+        <v>10.465116279069768</v>
+      </c>
+      <c r="H38">
+        <v>44562</v>
+      </c>
+      <c r="I38">
+        <v>45015</v>
       </c>
       <c r="J38">
-        <v>1193</v>
+        <v>453</v>
       </c>
       <c r="K38">
-        <v>170</v>
-      </c>
-      <c r="L38" t="e">
-        <v>#DIV/0!</v>
+        <v>45</v>
+      </c>
+      <c r="L38">
+        <v>9.9337748344370862</v>
+      </c>
+      <c r="M38">
+        <v>27620</v>
       </c>
       <c r="N38">
-        <v>4672600</v>
+        <v>1242900</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -2038,46 +2085,46 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39">
-        <v>185405</v>
+        <v>185835</v>
       </c>
       <c r="D39">
-        <v>185835</v>
+        <v>186235</v>
       </c>
       <c r="E39">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="F39">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G39">
-        <v>10.465116279069768</v>
+        <v>10</v>
       </c>
       <c r="H39">
-        <v>44562</v>
+        <v>45015</v>
       </c>
       <c r="I39">
-        <v>45015</v>
+        <v>45410</v>
       </c>
       <c r="J39">
-        <v>453</v>
+        <v>395</v>
       </c>
       <c r="K39">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L39">
-        <v>9.9337748344370862</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="M39">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N39">
-        <v>1242900</v>
+        <v>1101600</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -2085,93 +2132,72 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40">
-        <v>185835</v>
+        <v>186235</v>
       </c>
       <c r="D40">
-        <v>186235</v>
+        <v>186582</v>
       </c>
       <c r="E40">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="F40">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>12.680115273775217</v>
       </c>
       <c r="H40">
-        <v>45015</v>
+        <v>45410</v>
       </c>
       <c r="I40">
-        <v>45410</v>
+        <v>45787</v>
       </c>
       <c r="J40">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="K40">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L40">
-        <v>10.126582278481013</v>
+        <v>11.671087533156498</v>
       </c>
       <c r="M40">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N40">
-        <v>1101600</v>
+        <v>1198120</v>
       </c>
       <c r="R40">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A41" s="1">
-        <v>46247</v>
-      </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
-      <c r="C41">
-        <v>186235</v>
-      </c>
-      <c r="D41">
-        <v>186582</v>
-      </c>
       <c r="E41">
-        <v>347</v>
-      </c>
-      <c r="F41">
-        <v>44</v>
-      </c>
-      <c r="G41">
-        <v>12.680115273775217</v>
-      </c>
-      <c r="H41">
-        <v>45410</v>
-      </c>
-      <c r="I41">
-        <v>45787</v>
+        <v>0</v>
+      </c>
+      <c r="G41" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J41">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>44</v>
-      </c>
-      <c r="L41">
-        <v>11.671087533156498</v>
-      </c>
-      <c r="M41">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L41" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N41">
-        <v>1198120</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -2251,9 +2277,6 @@
       <c r="N44">
         <v>0</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
@@ -2300,6 +2323,9 @@
       <c r="N46">
         <v>0</v>
       </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B47" t="s">
@@ -2328,99 +2354,99 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B48" t="s">
-        <v>12</v>
+      <c r="D48" t="s">
+        <v>16</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="G48" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1225</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L48" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3542620</v>
       </c>
       <c r="R48">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D49" t="s">
-        <v>16</v>
+      <c r="A49" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49">
+        <v>162930</v>
+      </c>
+      <c r="D49">
+        <v>163211</v>
       </c>
       <c r="E49">
-        <v>1177</v>
-      </c>
-      <c r="G49" t="e">
-        <v>#DIV/0!</v>
+        <v>281</v>
+      </c>
+      <c r="F49">
+        <v>42</v>
+      </c>
+      <c r="G49">
+        <v>14.946619217081849</v>
+      </c>
+      <c r="H49">
+        <v>49086</v>
+      </c>
+      <c r="I49">
+        <v>49321</v>
       </c>
       <c r="J49">
-        <v>1225</v>
+        <v>235</v>
       </c>
       <c r="K49">
-        <v>129</v>
-      </c>
-      <c r="L49" t="e">
-        <v>#DIV/0!</v>
+        <v>42</v>
+      </c>
+      <c r="L49">
+        <v>17.872340425531917</v>
+      </c>
+      <c r="M49">
+        <v>27230</v>
       </c>
       <c r="N49">
-        <v>3542620</v>
+        <v>1143660</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A50" s="1">
-        <v>46248</v>
-      </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="C50">
-        <v>162930</v>
-      </c>
-      <c r="D50">
-        <v>163211</v>
-      </c>
       <c r="E50">
-        <v>281</v>
-      </c>
-      <c r="F50">
-        <v>42</v>
-      </c>
-      <c r="G50">
-        <v>14.946619217081849</v>
-      </c>
-      <c r="H50">
-        <v>49086</v>
-      </c>
-      <c r="I50">
-        <v>49321</v>
+        <v>0</v>
+      </c>
+      <c r="G50" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J50">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>42</v>
-      </c>
-      <c r="L50">
-        <v>17.872340425531917</v>
-      </c>
-      <c r="M50">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L50" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N50">
-        <v>1143660</v>
+        <v>0</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -2604,9 +2630,6 @@
       <c r="N57">
         <v>0</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B58" t="s">
@@ -2630,6 +2653,9 @@
       <c r="N58">
         <v>0</v>
       </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B59" t="s">
@@ -2658,52 +2684,73 @@
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B60" t="s">
-        <v>13</v>
+      <c r="D60" t="s">
+        <v>16</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="G60" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L60" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1143660</v>
       </c>
       <c r="R60">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D61" t="s">
-        <v>16</v>
+      <c r="A61" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61">
+        <v>165304</v>
+      </c>
+      <c r="D61">
+        <v>165596</v>
       </c>
       <c r="E61">
-        <v>281</v>
-      </c>
-      <c r="G61" t="e">
-        <v>#DIV/0!</v>
+        <v>292</v>
+      </c>
+      <c r="F61">
+        <v>48</v>
+      </c>
+      <c r="G61">
+        <v>16.43835616438356</v>
+      </c>
+      <c r="H61">
+        <v>38923</v>
+      </c>
+      <c r="I61">
+        <v>39254</v>
       </c>
       <c r="J61">
-        <v>235</v>
+        <v>331</v>
       </c>
       <c r="K61">
-        <v>42</v>
-      </c>
-      <c r="L61" t="e">
-        <v>#DIV/0!</v>
+        <v>48</v>
+      </c>
+      <c r="L61">
+        <v>14.501510574018129</v>
+      </c>
+      <c r="M61">
+        <v>27620</v>
       </c>
       <c r="N61">
-        <v>1143660</v>
+        <v>1325760</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -2711,46 +2758,46 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
       </c>
       <c r="C62">
-        <v>165304</v>
+        <v>165596</v>
       </c>
       <c r="D62">
-        <v>165596</v>
+        <v>165880</v>
       </c>
       <c r="E62">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F62">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G62">
-        <v>16.43835616438356</v>
+        <v>15.845070422535212</v>
       </c>
       <c r="H62">
-        <v>38923</v>
+        <v>39254</v>
       </c>
       <c r="I62">
-        <v>39254</v>
+        <v>39574</v>
       </c>
       <c r="J62">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="K62">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L62">
-        <v>14.501510574018129</v>
+        <v>14.0625</v>
       </c>
       <c r="M62">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N62">
-        <v>1325760</v>
+        <v>1239300</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -2758,46 +2805,46 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
       </c>
       <c r="C63">
-        <v>165596</v>
+        <v>165880</v>
       </c>
       <c r="D63">
-        <v>165880</v>
+        <v>166229</v>
       </c>
       <c r="E63">
-        <v>284</v>
+        <v>349</v>
       </c>
       <c r="F63">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G63">
-        <v>15.845070422535212</v>
+        <v>14.326647564469914</v>
       </c>
       <c r="H63">
-        <v>39254</v>
+        <v>39574</v>
       </c>
       <c r="I63">
-        <v>39574</v>
+        <v>39884</v>
       </c>
       <c r="J63">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="K63">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L63">
-        <v>14.0625</v>
+        <v>16.129032258064516</v>
       </c>
       <c r="M63">
         <v>27540</v>
       </c>
       <c r="N63">
-        <v>1239300</v>
+        <v>1377000</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -2805,93 +2852,72 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
       </c>
       <c r="C64">
-        <v>165880</v>
+        <v>166229</v>
       </c>
       <c r="D64">
-        <v>166229</v>
+        <v>166482</v>
       </c>
       <c r="E64">
-        <v>349</v>
+        <v>253</v>
       </c>
       <c r="F64">
         <v>50</v>
       </c>
       <c r="G64">
-        <v>14.326647564469914</v>
+        <v>19.762845849802371</v>
       </c>
       <c r="H64">
-        <v>39574</v>
+        <v>39884</v>
       </c>
       <c r="I64">
-        <v>39884</v>
+        <v>40153</v>
       </c>
       <c r="J64">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="K64">
         <v>50</v>
       </c>
       <c r="L64">
-        <v>16.129032258064516</v>
+        <v>18.587360594795538</v>
       </c>
       <c r="M64">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N64">
-        <v>1377000</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
+        <v>1361500</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A65" s="1">
-        <v>46252</v>
-      </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
-      <c r="C65">
-        <v>166229</v>
-      </c>
-      <c r="D65">
-        <v>166482</v>
-      </c>
       <c r="E65">
-        <v>253</v>
-      </c>
-      <c r="F65">
-        <v>50</v>
-      </c>
-      <c r="G65">
-        <v>19.762845849802371</v>
-      </c>
-      <c r="H65">
-        <v>39884</v>
-      </c>
-      <c r="I65">
-        <v>40153</v>
+        <v>0</v>
+      </c>
+      <c r="G65" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J65">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>50</v>
-      </c>
-      <c r="L65">
-        <v>18.587360594795538</v>
-      </c>
-      <c r="M65">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L65" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N65">
-        <v>1361500</v>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.15">
@@ -2999,52 +3025,73 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B70" t="s">
-        <v>15</v>
+      <c r="D70" t="s">
+        <v>16</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1178</v>
       </c>
       <c r="G70" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L70" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>5303560</v>
       </c>
       <c r="R70">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D71" t="s">
-        <v>16</v>
+      <c r="A71" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71">
+        <v>412813</v>
+      </c>
+      <c r="D71">
+        <v>413420</v>
       </c>
       <c r="E71">
-        <v>1178</v>
-      </c>
-      <c r="G71" t="e">
-        <v>#DIV/0!</v>
+        <v>607</v>
+      </c>
+      <c r="F71">
+        <v>80</v>
+      </c>
+      <c r="G71">
+        <v>13.179571663920923</v>
+      </c>
+      <c r="H71">
+        <v>44630</v>
+      </c>
+      <c r="I71">
+        <v>45250</v>
       </c>
       <c r="J71">
-        <v>1230</v>
+        <v>620</v>
       </c>
       <c r="K71">
-        <v>193</v>
-      </c>
-      <c r="L71" t="e">
-        <v>#DIV/0!</v>
+        <v>80</v>
+      </c>
+      <c r="L71">
+        <v>12.903225806451612</v>
+      </c>
+      <c r="M71">
+        <v>27540</v>
       </c>
       <c r="N71">
-        <v>5303560</v>
+        <v>2203200</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -3052,46 +3099,46 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
       </c>
       <c r="C72">
-        <v>412813</v>
+        <v>413420</v>
       </c>
       <c r="D72">
-        <v>413420</v>
+        <v>413937</v>
       </c>
       <c r="E72">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="F72">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G72">
-        <v>13.179571663920923</v>
+        <v>10.638297872340425</v>
       </c>
       <c r="H72">
-        <v>44630</v>
+        <v>45250</v>
       </c>
       <c r="I72">
-        <v>45250</v>
+        <v>45753</v>
       </c>
       <c r="J72">
-        <v>620</v>
+        <v>503</v>
       </c>
       <c r="K72">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="L72">
-        <v>12.903225806451612</v>
+        <v>10.934393638170974</v>
       </c>
       <c r="M72">
         <v>27540</v>
       </c>
       <c r="N72">
-        <v>2203200</v>
+        <v>1514700</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -3099,93 +3146,72 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
       </c>
       <c r="C73">
-        <v>413420</v>
+        <v>413937</v>
       </c>
       <c r="D73">
-        <v>413937</v>
+        <v>414394</v>
       </c>
       <c r="E73">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="F73">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G73">
-        <v>10.638297872340425</v>
+        <v>10.065645514223196</v>
       </c>
       <c r="H73">
-        <v>45250</v>
+        <v>45753</v>
       </c>
       <c r="I73">
-        <v>45753</v>
+        <v>46187</v>
       </c>
       <c r="J73">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="K73">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L73">
-        <v>10.934393638170974</v>
+        <v>10.599078341013826</v>
       </c>
       <c r="M73">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N73">
-        <v>1514700</v>
+        <v>1252580</v>
       </c>
       <c r="R73">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A74" s="1">
-        <v>46252</v>
-      </c>
       <c r="B74" t="s">
         <v>17</v>
       </c>
-      <c r="C74">
-        <v>413937</v>
-      </c>
-      <c r="D74">
-        <v>414394</v>
-      </c>
       <c r="E74">
-        <v>457</v>
-      </c>
-      <c r="F74">
-        <v>46</v>
-      </c>
-      <c r="G74">
-        <v>10.065645514223196</v>
-      </c>
-      <c r="H74">
-        <v>45753</v>
-      </c>
-      <c r="I74">
-        <v>46187</v>
+        <v>0</v>
+      </c>
+      <c r="G74" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J74">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>46</v>
-      </c>
-      <c r="L74">
-        <v>10.599078341013826</v>
-      </c>
-      <c r="M74">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L74" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N74">
-        <v>1252580</v>
+        <v>0</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -3296,52 +3322,52 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B79" t="s">
-        <v>17</v>
+      <c r="D79" t="s">
+        <v>16</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="G79" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="L79" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>4970480</v>
       </c>
       <c r="R79">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D80" t="s">
-        <v>16</v>
+      <c r="B80" t="s">
+        <v>18</v>
       </c>
       <c r="E80">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="G80" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J80">
-        <v>1557</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="L80" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N80">
-        <v>4970480</v>
+        <v>0</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -3351,20 +3377,26 @@
       <c r="B81" t="s">
         <v>18</v>
       </c>
+      <c r="D81">
+        <v>392889</v>
+      </c>
       <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="G81" t="e">
-        <v>#DIV/0!</v>
+        <v>392889</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>35946</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>35946</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
-      <c r="L81" t="e">
-        <v>#DIV/0!</v>
+      <c r="L81">
+        <v>0</v>
       </c>
       <c r="N81">
         <v>0</v>
@@ -3377,26 +3409,20 @@
       <c r="B82" t="s">
         <v>18</v>
       </c>
-      <c r="D82">
-        <v>392889</v>
-      </c>
       <c r="E82">
-        <v>392889</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>35946</v>
+        <v>0</v>
+      </c>
+      <c r="G82" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J82">
-        <v>35946</v>
+        <v>0</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
-      <c r="L82">
-        <v>0</v>
+      <c r="L82" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -3459,7 +3485,7 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B85" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3510,17 +3536,17 @@
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B87" t="s">
-        <v>35</v>
+      <c r="D87" t="s">
+        <v>16</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>392889</v>
       </c>
       <c r="G87" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>35946</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -3536,26 +3562,47 @@
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D88" t="s">
-        <v>16</v>
+      <c r="A88" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88">
+        <v>229032</v>
+      </c>
+      <c r="D88">
+        <v>229570</v>
       </c>
       <c r="E88">
-        <v>392889</v>
-      </c>
-      <c r="G88" t="e">
-        <v>#DIV/0!</v>
+        <v>538</v>
+      </c>
+      <c r="F88">
+        <v>60</v>
+      </c>
+      <c r="G88">
+        <v>11.152416356877323</v>
+      </c>
+      <c r="H88">
+        <v>38033</v>
+      </c>
+      <c r="I88">
+        <v>38515</v>
       </c>
       <c r="J88">
-        <v>35946</v>
+        <v>482</v>
       </c>
       <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88" t="e">
-        <v>#DIV/0!</v>
+        <v>60</v>
+      </c>
+      <c r="L88">
+        <v>12.448132780082988</v>
+      </c>
+      <c r="M88">
+        <v>27620</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1657200</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -3563,46 +3610,46 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B89" t="s">
         <v>19</v>
       </c>
       <c r="C89">
-        <v>229032</v>
+        <v>229570</v>
       </c>
       <c r="D89">
-        <v>229570</v>
+        <v>230050</v>
       </c>
       <c r="E89">
-        <v>538</v>
+        <v>480</v>
       </c>
       <c r="F89">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G89">
-        <v>11.152416356877323</v>
+        <v>14.374999999999998</v>
       </c>
       <c r="H89">
-        <v>38033</v>
+        <v>38515</v>
       </c>
       <c r="I89">
-        <v>38515</v>
+        <v>39015</v>
       </c>
       <c r="J89">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="K89">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L89">
-        <v>12.448132780082988</v>
+        <v>13.8</v>
       </c>
       <c r="M89">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N89">
-        <v>1657200</v>
+        <v>1900260</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -3610,93 +3657,72 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="s">
         <v>19</v>
       </c>
       <c r="C90">
-        <v>229570</v>
+        <v>230050</v>
       </c>
       <c r="D90">
-        <v>230050</v>
+        <v>230411</v>
       </c>
       <c r="E90">
-        <v>480</v>
+        <v>361</v>
       </c>
       <c r="F90">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G90">
-        <v>14.374999999999998</v>
+        <v>14.40443213296399</v>
       </c>
       <c r="H90">
-        <v>38515</v>
+        <v>39015</v>
       </c>
       <c r="I90">
-        <v>39015</v>
+        <v>39401</v>
       </c>
       <c r="J90">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="K90">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="L90">
-        <v>13.8</v>
+        <v>13.471502590673575</v>
       </c>
       <c r="M90">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N90">
-        <v>1900260</v>
+        <v>1415960</v>
       </c>
       <c r="R90">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A91" s="1">
-        <v>46248</v>
-      </c>
       <c r="B91" t="s">
         <v>19</v>
       </c>
-      <c r="C91">
-        <v>230050</v>
-      </c>
-      <c r="D91">
-        <v>230411</v>
-      </c>
       <c r="E91">
-        <v>361</v>
-      </c>
-      <c r="F91">
-        <v>52</v>
-      </c>
-      <c r="G91">
-        <v>14.40443213296399</v>
-      </c>
-      <c r="H91">
-        <v>39015</v>
-      </c>
-      <c r="I91">
-        <v>39401</v>
+        <v>0</v>
+      </c>
+      <c r="G91" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J91">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>52</v>
-      </c>
-      <c r="L91">
-        <v>13.471502590673575</v>
-      </c>
-      <c r="M91">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L91" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N91">
-        <v>1415960</v>
+        <v>0</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -3807,52 +3833,73 @@
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B96" t="s">
-        <v>19</v>
+      <c r="D96" t="s">
+        <v>16</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="G96" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="L96" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>4973420</v>
       </c>
       <c r="R96">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D97" t="s">
-        <v>16</v>
+      <c r="A97" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97">
+        <v>184593</v>
+      </c>
+      <c r="D97">
+        <v>185054</v>
       </c>
       <c r="E97">
-        <v>1379</v>
-      </c>
-      <c r="G97" t="e">
-        <v>#DIV/0!</v>
+        <v>461</v>
+      </c>
+      <c r="F97">
+        <v>65</v>
+      </c>
+      <c r="G97">
+        <v>14.099783080260304</v>
+      </c>
+      <c r="H97">
+        <v>39864</v>
+      </c>
+      <c r="I97">
+        <v>40321</v>
       </c>
       <c r="J97">
-        <v>1368</v>
+        <v>457</v>
       </c>
       <c r="K97">
-        <v>181</v>
-      </c>
-      <c r="L97" t="e">
-        <v>#DIV/0!</v>
+        <v>65</v>
+      </c>
+      <c r="L97">
+        <v>14.223194748358861</v>
+      </c>
+      <c r="M97">
+        <v>27620</v>
       </c>
       <c r="N97">
-        <v>4973420</v>
+        <v>1795300</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -3860,93 +3907,72 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="B98" t="s">
         <v>36</v>
       </c>
       <c r="C98">
-        <v>184593</v>
+        <v>185054</v>
       </c>
       <c r="D98">
-        <v>185054</v>
+        <v>185588</v>
       </c>
       <c r="E98">
-        <v>461</v>
+        <v>534</v>
       </c>
       <c r="F98">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G98">
-        <v>14.099783080260304</v>
+        <v>11.797752808988763</v>
       </c>
       <c r="H98">
-        <v>39864</v>
+        <v>40321</v>
       </c>
       <c r="I98">
-        <v>40321</v>
+        <v>40831</v>
       </c>
       <c r="J98">
-        <v>457</v>
+        <v>510</v>
       </c>
       <c r="K98">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L98">
-        <v>14.223194748358861</v>
+        <v>12.352941176470589</v>
       </c>
       <c r="M98">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N98">
-        <v>1795300</v>
+        <v>1735020</v>
       </c>
       <c r="R98">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A99" s="1">
-        <v>46246</v>
-      </c>
       <c r="B99" t="s">
         <v>36</v>
       </c>
-      <c r="C99">
-        <v>185054</v>
-      </c>
-      <c r="D99">
-        <v>185588</v>
-      </c>
       <c r="E99">
-        <v>534</v>
-      </c>
-      <c r="F99">
-        <v>63</v>
-      </c>
-      <c r="G99">
-        <v>11.797752808988763</v>
-      </c>
-      <c r="H99">
-        <v>40321</v>
-      </c>
-      <c r="I99">
-        <v>40831</v>
+        <v>0</v>
+      </c>
+      <c r="G99" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J99">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="K99">
-        <v>63</v>
-      </c>
-      <c r="L99">
-        <v>12.352941176470589</v>
-      </c>
-      <c r="M99">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L99" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N99">
-        <v>1735020</v>
+        <v>0</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -4031,52 +4057,73 @@
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B103" t="s">
-        <v>36</v>
+      <c r="D103" t="s">
+        <v>16</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>995</v>
       </c>
       <c r="G103" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L103" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>3530320</v>
       </c>
       <c r="R103">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D104" t="s">
-        <v>16</v>
+      <c r="A104" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104">
+        <v>138532</v>
+      </c>
+      <c r="D104">
+        <v>139023</v>
       </c>
       <c r="E104">
-        <v>995</v>
-      </c>
-      <c r="G104" t="e">
-        <v>#DIV/0!</v>
+        <v>491</v>
+      </c>
+      <c r="F104">
+        <v>57</v>
+      </c>
+      <c r="G104">
+        <v>11.608961303462321</v>
+      </c>
+      <c r="H104">
+        <v>42533</v>
+      </c>
+      <c r="I104">
+        <v>43000</v>
       </c>
       <c r="J104">
-        <v>967</v>
+        <v>467</v>
       </c>
       <c r="K104">
-        <v>128</v>
-      </c>
-      <c r="L104" t="e">
-        <v>#DIV/0!</v>
+        <v>57</v>
+      </c>
+      <c r="L104">
+        <v>12.205567451820128</v>
+      </c>
+      <c r="M104">
+        <v>27620</v>
       </c>
       <c r="N104">
-        <v>3530320</v>
+        <v>1574340</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -4084,93 +4131,72 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B105" t="s">
         <v>37</v>
       </c>
       <c r="C105">
-        <v>138532</v>
+        <v>139023</v>
       </c>
       <c r="D105">
-        <v>139023</v>
+        <v>139692</v>
       </c>
       <c r="E105">
-        <v>491</v>
+        <v>669</v>
       </c>
       <c r="F105">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G105">
-        <v>11.608961303462321</v>
+        <v>12.107623318385651</v>
       </c>
       <c r="H105">
-        <v>42533</v>
+        <v>43000</v>
       </c>
       <c r="I105">
-        <v>43000</v>
+        <v>43657</v>
       </c>
       <c r="J105">
-        <v>467</v>
+        <v>657</v>
       </c>
       <c r="K105">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="L105">
-        <v>12.205567451820128</v>
+        <v>12.328767123287671</v>
       </c>
       <c r="M105">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N105">
-        <v>1574340</v>
+        <v>2230740</v>
       </c>
       <c r="R105">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A106" s="1">
-        <v>46246</v>
-      </c>
       <c r="B106" t="s">
         <v>37</v>
       </c>
-      <c r="C106">
-        <v>139023</v>
-      </c>
-      <c r="D106">
-        <v>139692</v>
-      </c>
       <c r="E106">
-        <v>669</v>
-      </c>
-      <c r="F106">
-        <v>81</v>
-      </c>
-      <c r="G106">
-        <v>12.107623318385651</v>
-      </c>
-      <c r="H106">
-        <v>43000</v>
-      </c>
-      <c r="I106">
-        <v>43657</v>
+        <v>0</v>
+      </c>
+      <c r="G106" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J106">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>81</v>
-      </c>
-      <c r="L106">
-        <v>12.328767123287671</v>
-      </c>
-      <c r="M106">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L106" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N106">
-        <v>2230740</v>
+        <v>0</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -4281,52 +4307,70 @@
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B111" t="s">
-        <v>37</v>
+      <c r="D111" t="s">
+        <v>16</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="G111" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>3058</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="L111" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3805080</v>
       </c>
       <c r="R111">
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D112" t="s">
-        <v>16</v>
+      <c r="A112" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112">
+        <v>135150</v>
+      </c>
+      <c r="D112">
+        <v>135763</v>
       </c>
       <c r="E112">
-        <v>3150</v>
-      </c>
-      <c r="G112" t="e">
-        <v>#DIV/0!</v>
+        <v>613</v>
+      </c>
+      <c r="F112">
+        <v>74</v>
+      </c>
+      <c r="G112">
+        <v>12.071778140293638</v>
+      </c>
+      <c r="H112">
+        <v>132819</v>
+      </c>
+      <c r="I112">
+        <v>133400</v>
       </c>
       <c r="J112">
-        <v>3058</v>
-      </c>
-      <c r="K112">
-        <v>394</v>
-      </c>
-      <c r="L112" t="e">
-        <v>#DIV/0!</v>
+        <v>581</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>27620</v>
       </c>
       <c r="N112">
-        <v>3805080</v>
+        <v>2043880</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -4334,43 +4378,43 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B113" t="s">
         <v>38</v>
       </c>
       <c r="C113">
-        <v>135150</v>
+        <v>135763</v>
       </c>
       <c r="D113">
-        <v>135763</v>
+        <v>136252</v>
       </c>
       <c r="E113">
-        <v>613</v>
+        <v>489</v>
       </c>
       <c r="F113">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G113">
-        <v>12.071778140293638</v>
+        <v>12.678936605316974</v>
       </c>
       <c r="H113">
-        <v>132819</v>
+        <v>133400</v>
       </c>
       <c r="I113">
-        <v>133400</v>
+        <v>133925</v>
       </c>
       <c r="J113">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="M113">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N113">
-        <v>2043880</v>
+        <v>1707480</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -4378,87 +4422,66 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B114" t="s">
         <v>38</v>
       </c>
       <c r="C114">
-        <v>135763</v>
+        <v>136252</v>
       </c>
       <c r="D114">
-        <v>136252</v>
+        <v>136864</v>
       </c>
       <c r="E114">
-        <v>489</v>
+        <v>612</v>
       </c>
       <c r="F114">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G114">
-        <v>12.678936605316974</v>
+        <v>12.091503267973856</v>
       </c>
       <c r="H114">
-        <v>133400</v>
+        <v>133925</v>
       </c>
       <c r="I114">
-        <v>133925</v>
+        <v>134520</v>
       </c>
       <c r="J114">
-        <v>525</v>
+        <v>595</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N114">
-        <v>1707480</v>
+        <v>2015020</v>
       </c>
       <c r="R114">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A115" s="1">
-        <v>46251</v>
-      </c>
       <c r="B115" t="s">
         <v>38</v>
       </c>
-      <c r="C115">
-        <v>136252</v>
-      </c>
-      <c r="D115">
-        <v>136864</v>
-      </c>
       <c r="E115">
-        <v>612</v>
-      </c>
-      <c r="F115">
-        <v>74</v>
-      </c>
-      <c r="G115">
-        <v>12.091503267973856</v>
-      </c>
-      <c r="H115">
-        <v>133925</v>
-      </c>
-      <c r="I115">
-        <v>134520</v>
+        <v>0</v>
+      </c>
+      <c r="G115" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J115">
-        <v>595</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L115" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N115">
-        <v>2015020</v>
+        <v>0</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -4477,6 +4500,9 @@
       <c r="J116">
         <v>0</v>
       </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
       <c r="L116" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -4540,17 +4566,17 @@
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B119" t="s">
-        <v>38</v>
+      <c r="D119" t="s">
+        <v>16</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="G119" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>1701</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -4559,33 +4585,54 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>5766380</v>
       </c>
       <c r="R119">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D120" t="s">
-        <v>16</v>
+      <c r="A120" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B120" t="s">
+        <v>39</v>
+      </c>
+      <c r="C120">
+        <v>187232</v>
+      </c>
+      <c r="D120">
+        <v>187828</v>
       </c>
       <c r="E120">
-        <v>1714</v>
-      </c>
-      <c r="G120" t="e">
-        <v>#DIV/0!</v>
+        <v>596</v>
+      </c>
+      <c r="F120">
+        <v>69</v>
+      </c>
+      <c r="G120">
+        <v>11.577181208053691</v>
+      </c>
+      <c r="H120">
+        <v>30807</v>
+      </c>
+      <c r="I120">
+        <v>31401</v>
       </c>
       <c r="J120">
-        <v>1701</v>
+        <v>594</v>
       </c>
       <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120" t="e">
-        <v>#DIV/0!</v>
+        <v>69</v>
+      </c>
+      <c r="L120">
+        <v>11.616161616161616</v>
+      </c>
+      <c r="M120">
+        <v>27540</v>
       </c>
       <c r="N120">
-        <v>5766380</v>
+        <v>1900260</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -4593,46 +4640,46 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B121" t="s">
         <v>39</v>
       </c>
       <c r="C121">
-        <v>187232</v>
+        <v>187828</v>
       </c>
       <c r="D121">
-        <v>187828</v>
+        <v>188354</v>
       </c>
       <c r="E121">
-        <v>596</v>
+        <v>526</v>
       </c>
       <c r="F121">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G121">
-        <v>11.577181208053691</v>
+        <v>7.9847908745247151</v>
       </c>
       <c r="H121">
-        <v>30807</v>
+        <v>31401</v>
       </c>
       <c r="I121">
-        <v>31401</v>
+        <v>31911</v>
       </c>
       <c r="J121">
-        <v>594</v>
+        <v>510</v>
       </c>
       <c r="K121">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="L121">
-        <v>11.616161616161616</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="M121">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N121">
-        <v>1900260</v>
+        <v>1143660</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -4640,93 +4687,72 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B122" t="s">
         <v>39</v>
       </c>
       <c r="C122">
-        <v>187828</v>
+        <v>188354</v>
       </c>
       <c r="D122">
-        <v>188354</v>
+        <v>189039</v>
       </c>
       <c r="E122">
-        <v>526</v>
+        <v>685</v>
       </c>
       <c r="F122">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G122">
-        <v>7.9847908745247151</v>
+        <v>10.072992700729927</v>
       </c>
       <c r="H122">
-        <v>31401</v>
+        <v>31911</v>
       </c>
       <c r="I122">
-        <v>31911</v>
+        <v>32503</v>
       </c>
       <c r="J122">
-        <v>510</v>
+        <v>592</v>
       </c>
       <c r="K122">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L122">
-        <v>8.235294117647058</v>
+        <v>11.655405405405405</v>
       </c>
       <c r="M122">
         <v>27230</v>
       </c>
       <c r="N122">
-        <v>1143660</v>
+        <v>1878870</v>
       </c>
       <c r="R122">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A123" s="1">
-        <v>46252</v>
-      </c>
       <c r="B123" t="s">
         <v>39</v>
       </c>
-      <c r="C123">
-        <v>188354</v>
-      </c>
-      <c r="D123">
-        <v>189039</v>
-      </c>
       <c r="E123">
-        <v>685</v>
-      </c>
-      <c r="F123">
-        <v>69</v>
-      </c>
-      <c r="G123">
-        <v>10.072992700729927</v>
-      </c>
-      <c r="H123">
-        <v>31911</v>
-      </c>
-      <c r="I123">
-        <v>32503</v>
+        <v>0</v>
+      </c>
+      <c r="G123" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J123">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="K123">
-        <v>69</v>
-      </c>
-      <c r="L123">
-        <v>11.655405405405405</v>
-      </c>
-      <c r="M123">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L123" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N123">
-        <v>1878870</v>
+        <v>0</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -4811,131 +4837,128 @@
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B127" t="s">
-        <v>39</v>
+      <c r="D127" t="s">
+        <v>16</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>1807</v>
       </c>
       <c r="G127" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>1696</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L127" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>4922790</v>
       </c>
       <c r="R127">
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D128" t="s">
-        <v>16</v>
+      <c r="A128" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B128" t="s">
+        <v>60</v>
+      </c>
+      <c r="C128">
+        <v>156787</v>
+      </c>
+      <c r="D128">
+        <v>157424</v>
       </c>
       <c r="E128">
-        <v>1807</v>
-      </c>
-      <c r="G128" t="e">
-        <v>#DIV/0!</v>
+        <v>637</v>
+      </c>
+      <c r="F128">
+        <v>75</v>
+      </c>
+      <c r="G128">
+        <v>11.773940345368917</v>
       </c>
       <c r="J128">
-        <v>1696</v>
+        <v>0</v>
       </c>
       <c r="K128">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L128" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="M128">
+        <v>27620</v>
+      </c>
       <c r="N128">
-        <v>4922790</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
+        <v>2071500</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B129" t="s">
         <v>60</v>
       </c>
       <c r="C129">
-        <v>156787</v>
+        <v>157424</v>
       </c>
       <c r="D129">
-        <v>157424</v>
+        <v>158006</v>
       </c>
       <c r="E129">
-        <v>637</v>
+        <v>582</v>
       </c>
       <c r="F129">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G129">
-        <v>11.773940345368917</v>
+        <v>11.855670103092782</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L129" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="M129">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N129">
-        <v>2071500</v>
+        <v>1900260</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A130" s="1">
-        <v>46248</v>
-      </c>
       <c r="B130" t="s">
         <v>60</v>
       </c>
-      <c r="C130">
-        <v>157424</v>
-      </c>
-      <c r="D130">
-        <v>158006</v>
-      </c>
       <c r="E130">
-        <v>582</v>
-      </c>
-      <c r="F130">
-        <v>69</v>
-      </c>
-      <c r="G130">
-        <v>11.855670103092782</v>
+        <v>0</v>
+      </c>
+      <c r="G130" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L130" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="M130">
-        <v>27540</v>
-      </c>
       <c r="N130">
-        <v>1900260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.15">
@@ -5031,11 +5054,11 @@
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B135" t="s">
-        <v>60</v>
+      <c r="D135" t="s">
+        <v>16</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>1219</v>
       </c>
       <c r="G135" t="e">
         <v>#DIV/0!</v>
@@ -5044,21 +5067,21 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L135" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3971760</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D136" t="s">
-        <v>16</v>
+      <c r="B136" t="s">
+        <v>24</v>
       </c>
       <c r="E136">
-        <v>1219</v>
+        <v>0</v>
       </c>
       <c r="G136" t="e">
         <v>#DIV/0!</v>
@@ -5067,13 +5090,16 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L136" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N136">
-        <v>3971760</v>
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.15">
@@ -5193,9 +5219,6 @@
       <c r="J141">
         <v>0</v>
       </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
       <c r="L141" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -5222,9 +5245,6 @@
       <c r="L142" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
       <c r="R142">
         <v>0</v>
       </c>
@@ -5265,9 +5285,6 @@
       <c r="L144" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B145" t="s">
@@ -5304,8 +5321,8 @@
       </c>
     </row>
     <row r="147" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B147" t="s">
-        <v>24</v>
+      <c r="D147" t="s">
+        <v>16</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5316,13 +5333,22 @@
       <c r="J147">
         <v>0</v>
       </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
       <c r="L147" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="R147">
+        <v>0</v>
+      </c>
     </row>
     <row r="148" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D148" t="s">
-        <v>16</v>
+      <c r="B148" t="s">
+        <v>25</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5437,9 +5463,6 @@
       <c r="J152">
         <v>0</v>
       </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
       <c r="L152" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -5486,6 +5509,9 @@
       <c r="J154">
         <v>0</v>
       </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
       <c r="L154" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -5523,8 +5549,8 @@
       </c>
     </row>
     <row r="156" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B156" t="s">
-        <v>25</v>
+      <c r="D156" t="s">
+        <v>16</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5549,8 +5575,8 @@
       </c>
     </row>
     <row r="157" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D157" t="s">
-        <v>16</v>
+      <c r="B157" t="s">
+        <v>40</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5639,9 +5665,6 @@
       <c r="J160">
         <v>0</v>
       </c>
-      <c r="K160">
-        <v>0</v>
-      </c>
       <c r="L160" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -5688,6 +5711,9 @@
       <c r="J162">
         <v>0</v>
       </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
       <c r="L162" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -5751,8 +5777,8 @@
       </c>
     </row>
     <row r="165" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B165" t="s">
-        <v>40</v>
+      <c r="D165" t="s">
+        <v>16</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5777,8 +5803,8 @@
       </c>
     </row>
     <row r="166" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D166" t="s">
-        <v>16</v>
+      <c r="B166" t="s">
+        <v>26</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5899,9 +5925,6 @@
       <c r="L170" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
       <c r="R170">
         <v>0</v>
       </c>
@@ -5925,6 +5948,9 @@
       <c r="L171" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
       <c r="R171">
         <v>0</v>
       </c>
@@ -5982,8 +6008,8 @@
       </c>
     </row>
     <row r="174" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B174" t="s">
-        <v>26</v>
+      <c r="D174" t="s">
+        <v>16</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -6008,8 +6034,8 @@
       </c>
     </row>
     <row r="175" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D175" t="s">
-        <v>16</v>
+      <c r="B175" t="s">
+        <v>41</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -6027,9 +6053,6 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N175">
-        <v>0</v>
-      </c>
-      <c r="R175">
         <v>0</v>
       </c>
     </row>
@@ -6195,8 +6218,8 @@
       </c>
     </row>
     <row r="183" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B183" t="s">
-        <v>41</v>
+      <c r="D183" t="s">
+        <v>16</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6218,8 +6241,8 @@
       </c>
     </row>
     <row r="184" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="D184" t="s">
-        <v>16</v>
+      <c r="B184" t="s">
+        <v>28</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6402,8 +6425,8 @@
       </c>
     </row>
     <row r="192" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B192" t="s">
-        <v>28</v>
+      <c r="D192" t="s">
+        <v>16</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6425,8 +6448,8 @@
       </c>
     </row>
     <row r="193" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D193" t="s">
-        <v>16</v>
+      <c r="B193" t="s">
+        <v>29</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6444,6 +6467,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="R193">
         <v>0</v>
       </c>
     </row>
@@ -6518,9 +6544,6 @@
       <c r="L196" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N196">
-        <v>0</v>
-      </c>
       <c r="R196">
         <v>0</v>
       </c>
@@ -6544,6 +6567,9 @@
       <c r="L197" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
       <c r="R197">
         <v>0</v>
       </c>
@@ -6601,8 +6627,8 @@
       </c>
     </row>
     <row r="200" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B200" t="s">
-        <v>29</v>
+      <c r="D200" t="s">
+        <v>16</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6622,13 +6648,10 @@
       <c r="N200">
         <v>0</v>
       </c>
-      <c r="R200">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D201" t="s">
-        <v>16</v>
+      <c r="B201" t="s">
+        <v>30</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6786,10 +6809,13 @@
       <c r="N207">
         <v>0</v>
       </c>
+      <c r="R207">
+        <v>0</v>
+      </c>
     </row>
     <row r="208" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B208" t="s">
-        <v>30</v>
+      <c r="D208" t="s">
+        <v>16</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -6809,13 +6835,10 @@
       <c r="N208">
         <v>0</v>
       </c>
-      <c r="R208">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="D209" t="s">
-        <v>16</v>
+      <c r="B209" t="s">
+        <v>61</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -6975,8 +6998,8 @@
       </c>
     </row>
     <row r="216" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B216" t="s">
-        <v>61</v>
+      <c r="D216" t="s">
+        <v>16</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -6998,8 +7021,8 @@
       </c>
     </row>
     <row r="217" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="D217" t="s">
-        <v>16</v>
+      <c r="B217" t="s">
+        <v>33</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7159,8 +7182,8 @@
       </c>
     </row>
     <row r="224" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B224" t="s">
-        <v>33</v>
+      <c r="D224" t="s">
+        <v>16</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7182,8 +7205,8 @@
       </c>
     </row>
     <row r="225" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D225" t="s">
-        <v>16</v>
+      <c r="B225" t="s">
+        <v>34</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7343,8 +7366,8 @@
       </c>
     </row>
     <row r="232" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B232" t="s">
-        <v>34</v>
+      <c r="D232" t="s">
+        <v>16</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7366,80 +7389,92 @@
       </c>
     </row>
     <row r="233" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="D233" t="s">
-        <v>16</v>
-      </c>
-      <c r="E233">
-        <v>0</v>
-      </c>
-      <c r="G233" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J233">
-        <v>0</v>
-      </c>
-      <c r="K233">
-        <v>0</v>
-      </c>
-      <c r="L233" t="e">
-        <v>#DIV/0!</v>
-      </c>
       <c r="N233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="N234">
         <v>60839180</v>
       </c>
-      <c r="R234">
-        <v>0</v>
+      <c r="R233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="D235" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="236" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B236" t="s">
+        <v>1</v>
+      </c>
       <c r="D236" t="s">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="E236" t="s">
+        <v>3</v>
+      </c>
+      <c r="G236" t="s">
+        <v>4</v>
+      </c>
+      <c r="I236" t="s">
+        <v>5</v>
+      </c>
+      <c r="J236" t="s">
+        <v>3</v>
+      </c>
+      <c r="K236" t="s">
+        <v>6</v>
+      </c>
+      <c r="L236" t="s">
+        <v>4</v>
+      </c>
+      <c r="N236" t="s">
+        <v>7</v>
+      </c>
+      <c r="O236">
+        <v>1</v>
+      </c>
+      <c r="P236" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B237" t="s">
-        <v>1</v>
-      </c>
-      <c r="D237" t="s">
+        <v>42</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="G237" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
         <v>2</v>
       </c>
-      <c r="E237" t="s">
-        <v>3</v>
-      </c>
-      <c r="G237" t="s">
-        <v>4</v>
-      </c>
-      <c r="I237" t="s">
-        <v>5</v>
-      </c>
-      <c r="J237" t="s">
-        <v>3</v>
-      </c>
-      <c r="K237" t="s">
-        <v>6</v>
-      </c>
-      <c r="L237" t="s">
-        <v>4</v>
-      </c>
-      <c r="N237" t="s">
-        <v>7</v>
-      </c>
-      <c r="O237">
-        <v>1</v>
-      </c>
       <c r="P237" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>13300063.199999999</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>13300063.199999999</v>
       </c>
     </row>
     <row r="238" spans="2:18" x14ac:dyDescent="0.15">
@@ -7465,16 +7500,16 @@
         <v>0</v>
       </c>
       <c r="O238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P238" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q238">
-        <v>13300063.199999999</v>
+        <v>5999864.4000000004</v>
       </c>
       <c r="R238">
-        <v>13300063.199999999</v>
+        <v>5999864.4000000004</v>
       </c>
     </row>
     <row r="239" spans="2:18" x14ac:dyDescent="0.15">
@@ -7487,29 +7522,32 @@
       <c r="G239" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="I239">
+        <v>424372</v>
+      </c>
       <c r="J239">
-        <v>0</v>
+        <v>424372</v>
       </c>
       <c r="K239">
         <v>0</v>
       </c>
-      <c r="L239" t="e">
-        <v>#DIV/0!</v>
+      <c r="L239">
+        <v>0</v>
       </c>
       <c r="N239">
         <v>0</v>
       </c>
       <c r="O239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P239" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q239">
-        <v>5999864.4000000004</v>
+        <v>0</v>
       </c>
       <c r="R239">
-        <v>5999864.4000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="2:18" x14ac:dyDescent="0.15">
@@ -7522,32 +7560,29 @@
       <c r="G240" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="I240">
-        <v>424372</v>
-      </c>
       <c r="J240">
-        <v>424372</v>
+        <v>0</v>
       </c>
       <c r="K240">
         <v>0</v>
       </c>
-      <c r="L240">
-        <v>0</v>
+      <c r="L240" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N240">
         <v>0</v>
       </c>
       <c r="O240">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P240" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>6700482</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>6700482</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.15">
@@ -7573,21 +7608,21 @@
         <v>0</v>
       </c>
       <c r="O241">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P241" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q241">
-        <v>6700482</v>
+        <v>14979893.899999999</v>
       </c>
       <c r="R241">
-        <v>6700482</v>
+        <v>14979893.899999999</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B242" t="s">
-        <v>42</v>
+      <c r="D242" t="s">
+        <v>16</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -7596,7 +7631,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J242">
-        <v>0</v>
+        <v>424372</v>
       </c>
       <c r="K242">
         <v>0</v>
@@ -7608,101 +7643,122 @@
         <v>0</v>
       </c>
       <c r="O242">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P242" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q242">
-        <v>14979893.899999999</v>
+        <v>8179930.7999999998</v>
       </c>
       <c r="R242">
-        <v>14979893.899999999</v>
+        <v>8179930.7999999998</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D243" t="s">
-        <v>16</v>
+      <c r="A243" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B243" t="s">
+        <v>49</v>
+      </c>
+      <c r="C243">
+        <v>520429</v>
+      </c>
+      <c r="D243">
+        <v>521210</v>
       </c>
       <c r="E243">
-        <v>0</v>
-      </c>
-      <c r="G243" t="e">
-        <v>#DIV/0!</v>
+        <v>781</v>
+      </c>
+      <c r="F243">
+        <v>253.44</v>
+      </c>
+      <c r="G243">
+        <v>32.450704225352112</v>
+      </c>
+      <c r="H243">
+        <v>519737</v>
+      </c>
+      <c r="I243">
+        <v>520489</v>
       </c>
       <c r="J243">
-        <v>424372</v>
+        <v>752</v>
       </c>
       <c r="K243">
-        <v>0</v>
-      </c>
-      <c r="L243" t="e">
-        <v>#DIV/0!</v>
+        <v>253.44</v>
+      </c>
+      <c r="L243">
+        <v>33.702127659574465</v>
+      </c>
+      <c r="M243">
+        <v>27620</v>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>7000012.7999999998</v>
       </c>
       <c r="O243">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P243" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q243">
-        <v>8179930.7999999998</v>
+        <v>0</v>
       </c>
       <c r="R243">
-        <v>8179930.7999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="B244" t="s">
         <v>49</v>
       </c>
       <c r="C244">
-        <v>520429</v>
+        <v>521210</v>
       </c>
       <c r="D244">
-        <v>521210</v>
+        <v>521904</v>
       </c>
       <c r="E244">
-        <v>781</v>
+        <v>694</v>
       </c>
       <c r="F244">
-        <v>253.44</v>
+        <v>228.76</v>
       </c>
       <c r="G244">
-        <v>32.450704225352112</v>
+        <v>32.962536023054753</v>
       </c>
       <c r="H244">
-        <v>519737</v>
+        <v>520489</v>
       </c>
       <c r="I244">
-        <v>520489</v>
+        <v>521178</v>
       </c>
       <c r="J244">
-        <v>752</v>
+        <v>689</v>
       </c>
       <c r="K244">
-        <v>253.44</v>
+        <v>228.76</v>
       </c>
       <c r="L244">
-        <v>33.702127659574465</v>
+        <v>33.20174165457184</v>
       </c>
       <c r="M244">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N244">
-        <v>7000012.7999999998</v>
+        <v>6300050.3999999994</v>
       </c>
       <c r="O244">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P244" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -7712,53 +7768,32 @@
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A245" s="1">
-        <v>46245</v>
-      </c>
       <c r="B245" t="s">
         <v>49</v>
       </c>
-      <c r="C245">
-        <v>521210</v>
-      </c>
-      <c r="D245">
-        <v>521904</v>
-      </c>
       <c r="E245">
-        <v>694</v>
-      </c>
-      <c r="F245">
-        <v>228.76</v>
-      </c>
-      <c r="G245">
-        <v>32.962536023054753</v>
-      </c>
-      <c r="H245">
-        <v>520489</v>
-      </c>
-      <c r="I245">
-        <v>521178</v>
+        <v>0</v>
+      </c>
+      <c r="G245" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J245">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="K245">
-        <v>228.76</v>
-      </c>
-      <c r="L245">
-        <v>33.20174165457184</v>
-      </c>
-      <c r="M245">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L245" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N245">
-        <v>6300050.3999999994</v>
+        <v>0</v>
       </c>
       <c r="O245">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P245" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -7790,16 +7825,16 @@
         <v>0</v>
       </c>
       <c r="O246">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P246" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>15400820.300000001</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>15400820.300000001</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.15">
@@ -7825,16 +7860,16 @@
         <v>0</v>
       </c>
       <c r="O247">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P247" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q247">
-        <v>15400820.300000001</v>
+        <v>14759730.199999999</v>
       </c>
       <c r="R247">
-        <v>15400820.300000001</v>
+        <v>14759730.199999999</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.15">
@@ -7860,133 +7895,130 @@
         <v>0</v>
       </c>
       <c r="O248">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P248" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="Q248">
-        <v>14759730.199999999</v>
+        <v>0</v>
       </c>
       <c r="R248">
-        <v>14759730.199999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B249" t="s">
-        <v>49</v>
+      <c r="D249" t="s">
+        <v>16</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="G249" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="K249">
-        <v>0</v>
+        <v>482.2</v>
       </c>
       <c r="L249" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>13300063.199999999</v>
       </c>
       <c r="O249">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P249" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>18600094.399999999</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>18600094.399999999</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D250" t="s">
-        <v>16</v>
+      <c r="A250" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B250" t="s">
+        <v>44</v>
       </c>
       <c r="E250">
-        <v>1475</v>
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>217.86</v>
       </c>
       <c r="G250" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="H250">
+        <v>9745</v>
+      </c>
+      <c r="I250">
+        <v>10071</v>
+      </c>
       <c r="J250">
-        <v>1441</v>
-      </c>
-      <c r="K250">
-        <v>482.2</v>
-      </c>
-      <c r="L250" t="e">
-        <v>#DIV/0!</v>
+        <v>326</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>27540</v>
       </c>
       <c r="N250">
-        <v>13300063.199999999</v>
+        <v>5999864.4000000004</v>
       </c>
       <c r="O250">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P250" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q250">
-        <v>18600094.399999999</v>
+        <v>6249927.5999999996</v>
       </c>
       <c r="R250">
-        <v>18600094.399999999</v>
+        <v>6249927.5999999996</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A251" s="1">
-        <v>46241</v>
-      </c>
       <c r="B251" t="s">
         <v>44</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
-      <c r="F251">
-        <v>217.86</v>
-      </c>
       <c r="G251" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="H251">
-        <v>9745</v>
-      </c>
-      <c r="I251">
-        <v>10071</v>
-      </c>
       <c r="J251">
-        <v>326</v>
-      </c>
-      <c r="L251">
-        <v>0</v>
-      </c>
-      <c r="M251">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L251" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N251">
-        <v>5999864.4000000004</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P251" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q251">
-        <v>6249927.5999999996</v>
+        <v>0</v>
       </c>
       <c r="R251">
-        <v>6249927.5999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.15">
@@ -8008,17 +8040,11 @@
       <c r="N252">
         <v>0</v>
       </c>
-      <c r="O252">
+      <c r="P252" t="s">
         <v>16</v>
       </c>
-      <c r="P252" t="s">
-        <v>56</v>
-      </c>
       <c r="Q252">
-        <v>0</v>
-      </c>
-      <c r="R252">
-        <v>0</v>
+        <v>104170806.79999998</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.15">
@@ -8040,12 +8066,6 @@
       <c r="N253">
         <v>0</v>
       </c>
-      <c r="P253" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q253">
-        <v>104170806.79999998</v>
-      </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B254" t="s">
@@ -8068,8 +8088,8 @@
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B255" t="s">
-        <v>44</v>
+      <c r="D255" t="s">
+        <v>16</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8078,18 +8098,21 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J255">
+        <v>326</v>
+      </c>
+      <c r="K255">
         <v>0</v>
       </c>
       <c r="L255" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>5999864.4000000004</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D256" t="s">
-        <v>16</v>
+      <c r="B256" t="s">
+        <v>45</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8098,7 +8121,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J256">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="K256">
         <v>0</v>
@@ -8107,7 +8130,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="N256">
-        <v>5999864.4000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.15">
@@ -8203,8 +8226,8 @@
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B261" t="s">
-        <v>45</v>
+      <c r="D261" t="s">
+        <v>16</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8226,11 +8249,14 @@
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D262" t="s">
-        <v>16</v>
-      </c>
-      <c r="E262">
-        <v>0</v>
+      <c r="A262" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B262" t="s">
+        <v>46</v>
+      </c>
+      <c r="F262">
+        <v>243.3</v>
       </c>
       <c r="G262" t="e">
         <v>#DIV/0!</v>
@@ -8239,24 +8265,24 @@
         <v>0</v>
       </c>
       <c r="K262">
-        <v>0</v>
+        <v>243.3</v>
       </c>
       <c r="L262" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="M262">
+        <v>27540</v>
+      </c>
       <c r="N262">
-        <v>0</v>
+        <v>6700482</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A263" s="1">
-        <v>46246</v>
-      </c>
       <c r="B263" t="s">
         <v>46</v>
       </c>
-      <c r="F263">
-        <v>243.3</v>
+      <c r="E263">
+        <v>0</v>
       </c>
       <c r="G263" t="e">
         <v>#DIV/0!</v>
@@ -8265,16 +8291,13 @@
         <v>0</v>
       </c>
       <c r="K263">
-        <v>243.3</v>
+        <v>0</v>
       </c>
       <c r="L263" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="M263">
-        <v>27540</v>
-      </c>
       <c r="N263">
-        <v>6700482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.15">
@@ -8347,8 +8370,8 @@
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B267" t="s">
-        <v>46</v>
+      <c r="D267" t="s">
+        <v>16</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8360,212 +8383,212 @@
         <v>0</v>
       </c>
       <c r="K267">
-        <v>0</v>
+        <v>243.3</v>
       </c>
       <c r="L267" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>6700482</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D268" t="s">
-        <v>16</v>
+      <c r="A268" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B268" t="s">
+        <v>47</v>
+      </c>
+      <c r="C268">
+        <v>316477</v>
+      </c>
+      <c r="D268">
+        <v>316935</v>
       </c>
       <c r="E268">
-        <v>0</v>
-      </c>
-      <c r="G268" t="e">
-        <v>#DIV/0!</v>
+        <v>458</v>
+      </c>
+      <c r="F268">
+        <v>144.82</v>
+      </c>
+      <c r="G268">
+        <v>31.620087336244541</v>
+      </c>
+      <c r="H268">
+        <v>30310</v>
+      </c>
+      <c r="I268">
+        <v>30583</v>
       </c>
       <c r="J268">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="K268">
-        <v>243.3</v>
-      </c>
-      <c r="L268" t="e">
-        <v>#DIV/0!</v>
+        <v>144.82</v>
+      </c>
+      <c r="L268">
+        <v>53.047619047619044</v>
+      </c>
+      <c r="M268">
+        <v>27620</v>
       </c>
       <c r="N268">
-        <v>6700482</v>
+        <v>3999928.4</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B269" t="s">
         <v>47</v>
       </c>
       <c r="C269">
-        <v>316477</v>
+        <v>316935</v>
       </c>
       <c r="D269">
-        <v>316935</v>
+        <v>317353</v>
       </c>
       <c r="E269">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="F269">
-        <v>144.82</v>
+        <v>139.07</v>
       </c>
       <c r="G269">
-        <v>31.620087336244541</v>
+        <v>33.270334928229659</v>
       </c>
       <c r="H269">
-        <v>30310</v>
+        <v>30583</v>
       </c>
       <c r="I269">
-        <v>30583</v>
+        <v>30993</v>
       </c>
       <c r="J269">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="K269">
-        <v>144.82</v>
+        <v>139.07</v>
       </c>
       <c r="L269">
-        <v>53.047619047619044</v>
+        <v>33.919512195121946</v>
       </c>
       <c r="M269">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N269">
-        <v>3999928.4</v>
+        <v>3829987.8</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B270" t="s">
         <v>47</v>
       </c>
       <c r="C270">
-        <v>316935</v>
+        <v>317353</v>
       </c>
       <c r="D270">
-        <v>317353</v>
+        <v>317737</v>
       </c>
       <c r="E270">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="F270">
-        <v>139.07</v>
+        <v>122.73</v>
       </c>
       <c r="G270">
-        <v>33.270334928229659</v>
+        <v>31.960937500000004</v>
       </c>
       <c r="H270">
-        <v>30583</v>
+        <v>30993</v>
       </c>
       <c r="I270">
-        <v>30993</v>
+        <v>31323</v>
       </c>
       <c r="J270">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="K270">
-        <v>139.07</v>
+        <v>122.73</v>
       </c>
       <c r="L270">
-        <v>33.919512195121946</v>
+        <v>37.190909090909088</v>
       </c>
       <c r="M270">
         <v>27540</v>
       </c>
       <c r="N270">
-        <v>3829987.8</v>
+        <v>3379984.2</v>
       </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B271" t="s">
         <v>47</v>
       </c>
       <c r="C271">
-        <v>317353</v>
+        <v>317737</v>
       </c>
       <c r="D271">
-        <v>317737</v>
+        <v>318183</v>
       </c>
       <c r="E271">
-        <v>384</v>
+        <v>446</v>
       </c>
       <c r="F271">
-        <v>122.73</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="G271">
-        <v>31.960937500000004</v>
+        <v>31.042600896860982</v>
       </c>
       <c r="H271">
-        <v>30993</v>
+        <v>31323</v>
       </c>
       <c r="I271">
-        <v>31323</v>
+        <v>31733</v>
       </c>
       <c r="J271">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="K271">
-        <v>122.73</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="L271">
-        <v>37.190909090909088</v>
+        <v>33.768292682926827</v>
       </c>
       <c r="M271">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N271">
-        <v>3379984.2</v>
+        <v>3769993.4999999995</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A272" s="1">
-        <v>46251</v>
-      </c>
       <c r="B272" t="s">
         <v>47</v>
       </c>
-      <c r="C272">
-        <v>317737</v>
-      </c>
-      <c r="D272">
-        <v>318183</v>
-      </c>
       <c r="E272">
-        <v>446</v>
-      </c>
-      <c r="F272">
-        <v>138.44999999999999</v>
-      </c>
-      <c r="G272">
-        <v>31.042600896860982</v>
-      </c>
-      <c r="H272">
-        <v>31323</v>
-      </c>
-      <c r="I272">
-        <v>31733</v>
+        <v>0</v>
+      </c>
+      <c r="G272" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J272">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="K272">
-        <v>138.44999999999999</v>
-      </c>
-      <c r="L272">
-        <v>33.768292682926827</v>
-      </c>
-      <c r="M272">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L272" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N272">
-        <v>3769993.4999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="2:14" x14ac:dyDescent="0.15">
@@ -8592,49 +8615,49 @@
       </c>
     </row>
     <row r="274" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B274" t="s">
-        <v>47</v>
+      <c r="D274" t="s">
+        <v>16</v>
       </c>
       <c r="E274">
-        <v>0</v>
+        <v>1706</v>
       </c>
       <c r="G274" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J274">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="K274">
-        <v>0</v>
+        <v>545.06999999999994</v>
       </c>
       <c r="L274" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>14979893.899999999</v>
       </c>
     </row>
     <row r="275" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="D275" t="s">
-        <v>16</v>
+      <c r="B275" t="s">
+        <v>57</v>
       </c>
       <c r="E275">
-        <v>1706</v>
+        <v>0</v>
       </c>
       <c r="G275" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J275">
-        <v>1423</v>
+        <v>0</v>
       </c>
       <c r="K275">
-        <v>545.06999999999994</v>
+        <v>0</v>
       </c>
       <c r="L275" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N275">
-        <v>14979893.899999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="2:14" x14ac:dyDescent="0.15">
@@ -8799,9 +8822,6 @@
       </c>
     </row>
     <row r="283" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B283" t="s">
-        <v>57</v>
-      </c>
       <c r="E283">
         <v>0</v>
       </c>
@@ -8822,6 +8842,9 @@
       </c>
     </row>
     <row r="284" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B284" t="s">
+        <v>50</v>
+      </c>
       <c r="E284">
         <v>0</v>
       </c>
@@ -8829,9 +8852,6 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J284">
-        <v>0</v>
-      </c>
-      <c r="K284">
         <v>0</v>
       </c>
       <c r="L284" t="e">
@@ -8854,6 +8874,9 @@
       <c r="J285">
         <v>0</v>
       </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
       <c r="L285" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -8957,12 +8980,6 @@
       <c r="B290" t="s">
         <v>50</v>
       </c>
-      <c r="E290">
-        <v>0</v>
-      </c>
-      <c r="G290" t="e">
-        <v>#DIV/0!</v>
-      </c>
       <c r="J290">
         <v>0</v>
       </c>
@@ -8980,6 +8997,12 @@
       <c r="B291" t="s">
         <v>50</v>
       </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="G291" t="e">
+        <v>#DIV/0!</v>
+      </c>
       <c r="J291">
         <v>0</v>
       </c>
@@ -8994,8 +9017,8 @@
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B292" t="s">
-        <v>50</v>
+      <c r="D292" t="s">
+        <v>16</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9017,8 +9040,8 @@
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D293" t="s">
-        <v>16</v>
+      <c r="B293" t="s">
+        <v>51</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9098,9 +9121,6 @@
       <c r="J296">
         <v>0</v>
       </c>
-      <c r="K296">
-        <v>0</v>
-      </c>
       <c r="L296" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -9121,6 +9141,9 @@
       <c r="J297">
         <v>0</v>
       </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
       <c r="L297" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -9198,8 +9221,8 @@
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B301" t="s">
-        <v>51</v>
+      <c r="D301" t="s">
+        <v>16</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -9221,70 +9244,70 @@
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D302" t="s">
-        <v>16</v>
+      <c r="A302" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B302" t="s">
+        <v>66</v>
+      </c>
+      <c r="C302">
+        <v>163334</v>
+      </c>
+      <c r="D302">
+        <v>164262</v>
       </c>
       <c r="E302">
-        <v>0</v>
-      </c>
-      <c r="G302" t="e">
-        <v>#DIV/0!</v>
+        <v>928</v>
+      </c>
+      <c r="F302">
+        <v>297.02</v>
+      </c>
+      <c r="G302">
+        <v>32.006465517241381</v>
+      </c>
+      <c r="H302">
+        <v>162903</v>
+      </c>
+      <c r="I302">
+        <v>163808</v>
       </c>
       <c r="J302">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="K302">
-        <v>0</v>
-      </c>
-      <c r="L302" t="e">
-        <v>#DIV/0!</v>
+        <v>297.02</v>
+      </c>
+      <c r="L302">
+        <v>32.819889502762429</v>
+      </c>
+      <c r="M302">
+        <v>27540</v>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>8179930.7999999998</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A303" s="1">
-        <v>46242</v>
-      </c>
       <c r="B303" t="s">
         <v>66</v>
       </c>
-      <c r="C303">
-        <v>163334</v>
-      </c>
-      <c r="D303">
-        <v>164262</v>
-      </c>
       <c r="E303">
-        <v>928</v>
-      </c>
-      <c r="F303">
-        <v>297.02</v>
-      </c>
-      <c r="G303">
-        <v>32.006465517241381</v>
-      </c>
-      <c r="H303">
-        <v>162903</v>
-      </c>
-      <c r="I303">
-        <v>163808</v>
+        <v>0</v>
+      </c>
+      <c r="G303" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J303">
-        <v>905</v>
+        <v>0</v>
       </c>
       <c r="K303">
-        <v>297.02</v>
-      </c>
-      <c r="L303">
-        <v>32.819889502762429</v>
-      </c>
-      <c r="M303">
-        <v>27540</v>
+        <v>0</v>
+      </c>
+      <c r="L303" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N303">
-        <v>8179930.7999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.15">
@@ -9380,181 +9403,181 @@
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B308" t="s">
-        <v>66</v>
+      <c r="D308" t="s">
+        <v>16</v>
       </c>
       <c r="E308">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="G308" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J308">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="K308">
-        <v>0</v>
+        <v>297.02</v>
       </c>
       <c r="L308" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>8179930.7999999998</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D309" t="s">
-        <v>16</v>
+      <c r="A309" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B309" t="s">
+        <v>64</v>
+      </c>
+      <c r="C309">
+        <v>19578</v>
+      </c>
+      <c r="D309">
+        <v>20281</v>
       </c>
       <c r="E309">
-        <v>928</v>
-      </c>
-      <c r="G309" t="e">
-        <v>#DIV/0!</v>
+        <v>703</v>
+      </c>
+      <c r="F309">
+        <v>191.91</v>
+      </c>
+      <c r="G309">
+        <v>27.298719772403985</v>
+      </c>
+      <c r="H309">
+        <v>4774</v>
+      </c>
+      <c r="I309">
+        <v>5477</v>
       </c>
       <c r="J309">
-        <v>905</v>
+        <v>703</v>
       </c>
       <c r="K309">
-        <v>297.02</v>
-      </c>
-      <c r="L309" t="e">
-        <v>#DIV/0!</v>
+        <v>191.91</v>
+      </c>
+      <c r="L309">
+        <v>27.298719772403985</v>
+      </c>
+      <c r="M309">
+        <v>27620</v>
       </c>
       <c r="N309">
-        <v>8179930.7999999998</v>
+        <v>5300554.2</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B310" t="s">
         <v>64</v>
       </c>
       <c r="C310">
-        <v>19578</v>
+        <v>20281</v>
       </c>
       <c r="D310">
-        <v>20281</v>
+        <v>20848</v>
       </c>
       <c r="E310">
-        <v>703</v>
+        <v>567</v>
       </c>
       <c r="F310">
-        <v>191.91</v>
+        <v>174.29</v>
       </c>
       <c r="G310">
-        <v>27.298719772403985</v>
+        <v>30.738977072310401</v>
       </c>
       <c r="H310">
-        <v>4774</v>
+        <v>5477</v>
       </c>
       <c r="I310">
-        <v>5477</v>
+        <v>5979</v>
       </c>
       <c r="J310">
-        <v>703</v>
+        <v>502</v>
       </c>
       <c r="K310">
-        <v>191.91</v>
+        <v>174.29</v>
       </c>
       <c r="L310">
-        <v>27.298719772403985</v>
+        <v>34.719123505976093</v>
       </c>
       <c r="M310">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N310">
-        <v>5300554.2</v>
+        <v>4799946.5999999996</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B311" t="s">
         <v>64</v>
       </c>
       <c r="C311">
-        <v>20281</v>
+        <v>20848</v>
       </c>
       <c r="D311">
-        <v>20848</v>
+        <v>21499</v>
       </c>
       <c r="E311">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="F311">
-        <v>174.29</v>
+        <v>194.65</v>
       </c>
       <c r="G311">
-        <v>30.738977072310401</v>
+        <v>29.900153609831033</v>
       </c>
       <c r="H311">
-        <v>5477</v>
+        <v>5979</v>
       </c>
       <c r="I311">
-        <v>5979</v>
+        <v>6581</v>
       </c>
       <c r="J311">
-        <v>502</v>
+        <v>602</v>
       </c>
       <c r="K311">
-        <v>174.29</v>
+        <v>194.65</v>
       </c>
       <c r="L311">
-        <v>34.719123505976093</v>
+        <v>32.333887043189371</v>
       </c>
       <c r="M311">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N311">
-        <v>4799946.5999999996</v>
+        <v>5300319.5</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A312" s="1">
-        <v>46252</v>
-      </c>
       <c r="B312" t="s">
         <v>64</v>
       </c>
-      <c r="C312">
-        <v>20848</v>
-      </c>
-      <c r="D312">
-        <v>21499</v>
-      </c>
       <c r="E312">
-        <v>651</v>
-      </c>
-      <c r="F312">
-        <v>194.65</v>
-      </c>
-      <c r="G312">
-        <v>29.900153609831033</v>
-      </c>
-      <c r="H312">
-        <v>5979</v>
-      </c>
-      <c r="I312">
-        <v>6581</v>
+        <v>0</v>
+      </c>
+      <c r="G312" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J312">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="K312">
-        <v>194.65</v>
-      </c>
-      <c r="L312">
-        <v>32.333887043189371</v>
-      </c>
-      <c r="M312">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L312" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N312">
-        <v>5300319.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.15">
@@ -9650,184 +9673,184 @@
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B317" t="s">
-        <v>64</v>
+      <c r="D317" t="s">
+        <v>16</v>
       </c>
       <c r="E317">
-        <v>0</v>
+        <v>1921</v>
       </c>
       <c r="G317" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J317">
-        <v>0</v>
+        <v>1807</v>
       </c>
       <c r="K317">
-        <v>0</v>
+        <v>560.85</v>
       </c>
       <c r="L317" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>15400820.300000001</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D318" t="s">
-        <v>16</v>
+      <c r="A318" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B318" t="s">
+        <v>65</v>
+      </c>
+      <c r="C318">
+        <v>18591</v>
+      </c>
+      <c r="D318">
+        <v>19102</v>
       </c>
       <c r="E318">
-        <v>1921</v>
-      </c>
-      <c r="G318" t="e">
-        <v>#DIV/0!</v>
+        <v>511</v>
+      </c>
+      <c r="F318">
+        <v>173.78</v>
+      </c>
+      <c r="G318">
+        <v>34.007827788649706</v>
+      </c>
+      <c r="H318">
+        <v>18399</v>
+      </c>
+      <c r="I318">
+        <v>18915</v>
       </c>
       <c r="J318">
-        <v>1807</v>
+        <v>516</v>
       </c>
       <c r="K318">
-        <v>560.85</v>
-      </c>
-      <c r="L318" t="e">
-        <v>#DIV/0!</v>
+        <v>173.78</v>
+      </c>
+      <c r="L318">
+        <v>33.678294573643413</v>
+      </c>
+      <c r="M318">
+        <v>27620</v>
       </c>
       <c r="N318">
-        <v>15400820.300000001</v>
+        <v>4799803.5999999996</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B319" t="s">
         <v>65</v>
       </c>
       <c r="C319">
-        <v>18591</v>
+        <v>19102</v>
       </c>
       <c r="D319">
-        <v>19102</v>
+        <v>19690</v>
       </c>
       <c r="E319">
-        <v>511</v>
+        <v>588</v>
       </c>
       <c r="F319">
-        <v>173.78</v>
+        <v>180.1</v>
       </c>
       <c r="G319">
-        <v>34.007827788649706</v>
+        <v>30.629251700680271</v>
       </c>
       <c r="H319">
-        <v>18399</v>
+        <v>18915</v>
       </c>
       <c r="I319">
-        <v>18915</v>
+        <v>19415</v>
       </c>
       <c r="J319">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="K319">
-        <v>173.78</v>
+        <v>180.1</v>
       </c>
       <c r="L319">
-        <v>33.678294573643413</v>
+        <v>36.019999999999996</v>
       </c>
       <c r="M319">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N319">
-        <v>4799803.5999999996</v>
+        <v>4959954</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B320" t="s">
         <v>65</v>
       </c>
       <c r="C320">
-        <v>19102</v>
+        <v>19690</v>
       </c>
       <c r="D320">
-        <v>19690</v>
+        <v>20276</v>
       </c>
       <c r="E320">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F320">
-        <v>180.1</v>
+        <v>183.62</v>
       </c>
       <c r="G320">
-        <v>30.629251700680271</v>
+        <v>31.334470989761094</v>
       </c>
       <c r="H320">
-        <v>18915</v>
+        <v>19415</v>
       </c>
       <c r="I320">
-        <v>19415</v>
+        <v>20009</v>
       </c>
       <c r="J320">
-        <v>500</v>
+        <v>594</v>
       </c>
       <c r="K320">
-        <v>180.1</v>
+        <v>183.62</v>
       </c>
       <c r="L320">
-        <v>36.019999999999996</v>
+        <v>30.912457912457914</v>
       </c>
       <c r="M320">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N320">
-        <v>4959954</v>
-      </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A321" s="1">
-        <v>46252</v>
-      </c>
+        <v>4999972.6000000006</v>
+      </c>
+    </row>
+    <row r="321" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B321" t="s">
         <v>65</v>
       </c>
-      <c r="C321">
-        <v>19690</v>
-      </c>
-      <c r="D321">
-        <v>20276</v>
-      </c>
       <c r="E321">
-        <v>586</v>
-      </c>
-      <c r="F321">
-        <v>183.62</v>
-      </c>
-      <c r="G321">
-        <v>31.334470989761094</v>
-      </c>
-      <c r="H321">
-        <v>19415</v>
-      </c>
-      <c r="I321">
-        <v>20009</v>
+        <v>0</v>
+      </c>
+      <c r="G321" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J321">
-        <v>594</v>
+        <v>0</v>
       </c>
       <c r="K321">
-        <v>183.62</v>
-      </c>
-      <c r="L321">
-        <v>30.912457912457914</v>
-      </c>
-      <c r="M321">
-        <v>27230</v>
+        <v>0</v>
+      </c>
+      <c r="L321" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N321">
-        <v>4999972.6000000006</v>
-      </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B322" t="s">
         <v>65</v>
       </c>
@@ -9850,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="323" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B323" t="s">
         <v>65</v>
       </c>
@@ -9873,7 +9896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="324" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B324" t="s">
         <v>65</v>
       </c>
@@ -9896,7 +9919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="325" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B325" t="s">
         <v>65</v>
       </c>
@@ -9919,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="326" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B326" t="s">
         <v>65</v>
       </c>
@@ -9942,53 +9965,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B327" t="s">
-        <v>65</v>
+    <row r="327" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="D327" t="s">
+        <v>16</v>
       </c>
       <c r="E327">
-        <v>0</v>
+        <v>1685</v>
       </c>
       <c r="G327" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J327">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="K327">
-        <v>0</v>
+        <v>537.5</v>
       </c>
       <c r="L327" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N327">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D328" t="s">
-        <v>16</v>
+        <v>14759730.199999999</v>
+      </c>
+    </row>
+    <row r="328" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B328" t="s">
+        <v>53</v>
       </c>
       <c r="E328">
-        <v>1685</v>
+        <v>0</v>
       </c>
       <c r="G328" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="J328">
-        <v>1610</v>
+        <v>0</v>
       </c>
       <c r="K328">
-        <v>537.5</v>
+        <v>0</v>
       </c>
       <c r="L328" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N328">
-        <v>14759730.199999999</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B329" t="s">
         <v>53</v>
       </c>
@@ -10011,7 +10034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="330" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B330" t="s">
         <v>53</v>
       </c>
@@ -10034,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="331" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B331" t="s">
         <v>53</v>
       </c>
@@ -10057,7 +10080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="332" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B332" t="s">
         <v>53</v>
       </c>
@@ -10080,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="333" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B333" t="s">
         <v>53</v>
       </c>
@@ -10103,9 +10126,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B334" t="s">
-        <v>53</v>
+    <row r="334" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="D334" t="s">
+        <v>16</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -10126,9 +10149,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D335" t="s">
-        <v>16</v>
+    <row r="335" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B335" t="s">
+        <v>56</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -10149,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="336" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B336" t="s">
         <v>56</v>
       </c>
@@ -10265,8 +10288,8 @@
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B341" t="s">
-        <v>56</v>
+      <c r="D341" t="s">
+        <v>16</v>
       </c>
       <c r="E341">
         <v>0</v>
@@ -10288,140 +10311,140 @@
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D342" t="s">
-        <v>16</v>
+      <c r="A342" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B342" t="s">
+        <v>54</v>
+      </c>
+      <c r="C342">
+        <v>24811</v>
+      </c>
+      <c r="D342">
+        <v>25647</v>
       </c>
       <c r="E342">
-        <v>0</v>
-      </c>
-      <c r="G342" t="e">
-        <v>#DIV/0!</v>
+        <v>836</v>
+      </c>
+      <c r="F342">
+        <v>202.75</v>
+      </c>
+      <c r="G342">
+        <v>24.252392344497608</v>
       </c>
       <c r="J342">
         <v>0</v>
       </c>
       <c r="K342">
-        <v>0</v>
+        <v>202.75</v>
       </c>
       <c r="L342" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="M342">
+        <v>27620</v>
+      </c>
       <c r="N342">
-        <v>0</v>
+        <v>5599955</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B343" t="s">
         <v>54</v>
       </c>
       <c r="C343">
-        <v>24811</v>
+        <v>25647</v>
       </c>
       <c r="D343">
-        <v>25647</v>
+        <v>26520</v>
       </c>
       <c r="E343">
-        <v>836</v>
+        <v>873</v>
       </c>
       <c r="F343">
-        <v>202.75</v>
+        <v>243.29</v>
       </c>
       <c r="G343">
-        <v>24.252392344497608</v>
+        <v>27.868270332187855</v>
       </c>
       <c r="J343">
         <v>0</v>
       </c>
       <c r="K343">
-        <v>202.75</v>
+        <v>243.29</v>
       </c>
       <c r="L343" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="M343">
-        <v>27620</v>
+        <v>27540</v>
       </c>
       <c r="N343">
-        <v>5599955</v>
+        <v>6700206.5999999996</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="B344" t="s">
         <v>54</v>
       </c>
       <c r="C344">
-        <v>25647</v>
+        <v>26520</v>
       </c>
       <c r="D344">
-        <v>26520</v>
+        <v>27402</v>
       </c>
       <c r="E344">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="F344">
-        <v>243.29</v>
+        <v>231.36</v>
       </c>
       <c r="G344">
-        <v>27.868270332187855</v>
+        <v>26.231292517006803</v>
       </c>
       <c r="J344">
         <v>0</v>
       </c>
       <c r="K344">
-        <v>243.29</v>
+        <v>231.36</v>
       </c>
       <c r="L344" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="M344">
-        <v>27540</v>
+        <v>27230</v>
       </c>
       <c r="N344">
-        <v>6700206.5999999996</v>
+        <v>6299932.8000000007</v>
       </c>
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A345" s="1">
-        <v>46252</v>
-      </c>
       <c r="B345" t="s">
         <v>54</v>
       </c>
-      <c r="C345">
-        <v>26520</v>
-      </c>
-      <c r="D345">
-        <v>27402</v>
-      </c>
       <c r="E345">
-        <v>882</v>
-      </c>
-      <c r="F345">
-        <v>231.36</v>
-      </c>
-      <c r="G345">
-        <v>26.231292517006803</v>
+        <v>0</v>
+      </c>
+      <c r="G345" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="J345">
         <v>0</v>
       </c>
       <c r="K345">
-        <v>231.36</v>
+        <v>0</v>
       </c>
       <c r="L345" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="M345">
-        <v>27230</v>
-      </c>
       <c r="N345">
-        <v>6299932.8000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.15">
@@ -10469,6 +10492,9 @@
       <c r="N347">
         <v>0</v>
       </c>
+      <c r="R347">
+        <v>75</v>
+      </c>
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B348" t="s">
@@ -10492,9 +10518,6 @@
       <c r="N348">
         <v>0</v>
       </c>
-      <c r="R348">
-        <v>75</v>
-      </c>
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B349" t="s">
@@ -10543,11 +10566,11 @@
       </c>
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="B351" t="s">
-        <v>54</v>
+      <c r="D351" t="s">
+        <v>16</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>2591</v>
       </c>
       <c r="G351" t="e">
         <v>#DIV/0!</v>
@@ -10556,21 +10579,27 @@
         <v>0</v>
       </c>
       <c r="K351">
-        <v>0</v>
+        <v>677.4</v>
       </c>
       <c r="L351" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>18600094.399999999</v>
       </c>
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="D352" t="s">
-        <v>16</v>
+      <c r="A352" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B352" t="s">
+        <v>55</v>
       </c>
       <c r="E352">
-        <v>2591</v>
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>226.94</v>
       </c>
       <c r="G352" t="e">
         <v>#DIV/0!</v>
@@ -10579,28 +10608,25 @@
         <v>0</v>
       </c>
       <c r="K352">
-        <v>677.4</v>
+        <v>226.94</v>
       </c>
       <c r="L352" t="e">
         <v>#DIV/0!</v>
       </c>
+      <c r="M352">
+        <v>27540</v>
+      </c>
       <c r="N352">
-        <v>18600094.399999999</v>
-      </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A353" s="1">
-        <v>46242</v>
-      </c>
+        <v>6249927.5999999996</v>
+      </c>
+    </row>
+    <row r="353" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B353" t="s">
         <v>55</v>
       </c>
       <c r="E353">
         <v>0</v>
       </c>
-      <c r="F353">
-        <v>226.94</v>
-      </c>
       <c r="G353" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -10608,19 +10634,16 @@
         <v>0</v>
       </c>
       <c r="K353">
-        <v>226.94</v>
+        <v>0</v>
       </c>
       <c r="L353" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="M353">
-        <v>27540</v>
-      </c>
       <c r="N353">
-        <v>6249927.5999999996</v>
-      </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B354" t="s">
         <v>55</v>
       </c>
@@ -10643,7 +10666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="355" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B355" t="s">
         <v>55</v>
       </c>
@@ -10666,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="356" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B356" t="s">
         <v>55</v>
       </c>
@@ -10689,7 +10712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="357" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B357" t="s">
         <v>55</v>
       </c>
@@ -10712,9 +10735,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B358" t="s">
-        <v>55</v>
+    <row r="358" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="D358" t="s">
+        <v>16</v>
       </c>
       <c r="E358">
         <v>0</v>
@@ -10726,40 +10749,17 @@
         <v>0</v>
       </c>
       <c r="K358">
-        <v>0</v>
+        <v>226.94</v>
       </c>
       <c r="L358" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="N358">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="D359" t="s">
-        <v>16</v>
-      </c>
-      <c r="E359">
-        <v>0</v>
-      </c>
-      <c r="G359" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J359">
-        <v>0</v>
-      </c>
-      <c r="K359">
-        <v>226.94</v>
-      </c>
-      <c r="L359" t="e">
-        <v>#DIV/0!</v>
-      </c>
+        <v>6249927.5999999996</v>
+      </c>
+    </row>
+    <row r="359" spans="2:14" x14ac:dyDescent="0.15">
       <c r="N359">
-        <v>6249927.5999999996</v>
-      </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="N360">
         <v>104170806.79999998</v>
       </c>
     </row>
